--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -2132,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130180061</v>
+        <v>130180018</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,26 +2143,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2170,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490539</v>
+        <v>490478</v>
       </c>
       <c r="R14" t="n">
-        <v>7024036</v>
+        <v>7024001</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2210,7 +2215,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,7 +2224,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2240,12 +2244,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2263,42 +2267,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130180019</v>
+        <v>130180047</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>97704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490488</v>
+        <v>490586</v>
       </c>
       <c r="R15" t="n">
-        <v>7023990</v>
+        <v>7023926</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2355,32 +2355,13 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2398,38 +2379,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130180047</v>
+        <v>130180061</v>
       </c>
       <c r="B16" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2437,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490586</v>
+        <v>490539</v>
       </c>
       <c r="R16" t="n">
-        <v>7023926</v>
+        <v>7024036</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2477,7 +2457,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2493,6 +2473,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2510,7 +2510,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130180018</v>
+        <v>130180019</v>
       </c>
       <c r="B17" t="n">
         <v>57741</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490478</v>
+        <v>490488</v>
       </c>
       <c r="R17" t="n">
-        <v>7024001</v>
+        <v>7023990</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3059,49 +3059,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130180046</v>
+        <v>130180020</v>
       </c>
       <c r="B21" t="n">
-        <v>97702</v>
+        <v>57741</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490513</v>
+        <v>490494</v>
       </c>
       <c r="R21" t="n">
-        <v>7023984</v>
+        <v>7023983</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3138,7 +3146,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3147,13 +3155,32 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3171,7 +3198,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180020</v>
+        <v>130180014</v>
       </c>
       <c r="B22" t="n">
         <v>57741</v>
@@ -3204,24 +3231,20 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490494</v>
+        <v>490533</v>
       </c>
       <c r="R22" t="n">
-        <v>7023983</v>
+        <v>7024027</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3258,7 +3281,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
+          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3313,7 +3336,7 @@
         <v>130180051</v>
       </c>
       <c r="B23" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3548,42 +3571,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130180014</v>
+        <v>130180046</v>
       </c>
       <c r="B25" t="n">
-        <v>57741</v>
+        <v>97704</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3591,10 +3610,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490533</v>
+        <v>490513</v>
       </c>
       <c r="R25" t="n">
-        <v>7024027</v>
+        <v>7023984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3631,7 +3650,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3640,32 +3659,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130180031</v>
+        <v>130180029</v>
       </c>
       <c r="B27" t="n">
         <v>57741</v>
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490546</v>
+        <v>490543</v>
       </c>
       <c r="R27" t="n">
-        <v>7023885</v>
+        <v>7023888</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, i god mängd på en gran vid en hyggeskant. Troligen  skapade 2025.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3957,7 +3957,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130180029</v>
+        <v>130180031</v>
       </c>
       <c r="B28" t="n">
         <v>57741</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490543</v>
+        <v>490546</v>
       </c>
       <c r="R28" t="n">
-        <v>7023888</v>
+        <v>7023885</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i god mängd på en gran vid en hyggeskant. Troligen  skapade 2025.</t>
+          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4096,39 +4096,39 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130180042</v>
+        <v>130180009</v>
       </c>
       <c r="B29" t="n">
-        <v>80229</v>
+        <v>91641</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490679</v>
+        <v>490651</v>
       </c>
       <c r="R29" t="n">
-        <v>7023796</v>
+        <v>7024020</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>I en granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4198,22 +4198,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130180069</v>
+        <v>130180008</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>91641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4242,34 +4242,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490566</v>
+        <v>490598</v>
       </c>
       <c r="R30" t="n">
-        <v>7023937</v>
+        <v>7023986</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4306,7 +4313,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>I granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4315,8 +4322,34 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4333,39 +4366,39 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130180009</v>
+        <v>130180042</v>
       </c>
       <c r="B31" t="n">
-        <v>91639</v>
+        <v>80229</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4375,10 +4408,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490651</v>
+        <v>490679</v>
       </c>
       <c r="R31" t="n">
-        <v>7024020</v>
+        <v>7023796</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4415,7 +4448,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>I en granlåga i barrblandskog.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4435,22 +4468,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4468,10 +4501,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180033</v>
+        <v>130180069</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4479,42 +4512,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490591</v>
+        <v>490566</v>
       </c>
       <c r="R32" t="n">
-        <v>7023786</v>
+        <v>7023937</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4551,7 +4576,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4562,31 +4587,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4705,10 +4705,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130180008</v>
+        <v>130180033</v>
       </c>
       <c r="B34" t="n">
-        <v>91639</v>
+        <v>57741</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4716,28 +4716,29 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4747,10 +4748,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490598</v>
+        <v>490591</v>
       </c>
       <c r="R34" t="n">
-        <v>7023986</v>
+        <v>7023786</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4787,7 +4788,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>I granlåga i barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4796,7 +4797,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130180016</v>
+        <v>130180065</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4851,42 +4851,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490471</v>
+        <v>490576</v>
       </c>
       <c r="R35" t="n">
-        <v>7024008</v>
+        <v>7023998</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4923,7 +4915,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4934,31 +4926,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4975,10 +4942,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130180025</v>
+        <v>130180059</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4986,42 +4953,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490547</v>
+        <v>490614</v>
       </c>
       <c r="R36" t="n">
-        <v>7023930</v>
+        <v>7023878</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5058,7 +5017,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5069,31 +5028,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5110,7 +5044,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130180065</v>
+        <v>130180063</v>
       </c>
       <c r="B37" t="n">
         <v>79095</v>
@@ -5145,10 +5079,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490576</v>
+        <v>490561</v>
       </c>
       <c r="R37" t="n">
-        <v>7023998</v>
+        <v>7023986</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5185,7 +5119,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5212,10 +5146,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130180059</v>
+        <v>130180016</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5223,34 +5157,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490614</v>
+        <v>490471</v>
       </c>
       <c r="R38" t="n">
-        <v>7023878</v>
+        <v>7024008</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5287,7 +5229,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5298,6 +5240,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5314,10 +5281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130180063</v>
+        <v>130180025</v>
       </c>
       <c r="B39" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5325,34 +5292,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490561</v>
+        <v>490547</v>
       </c>
       <c r="R39" t="n">
-        <v>7023986</v>
+        <v>7023930</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5389,7 +5364,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5400,6 +5375,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -6029,10 +6029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130180060</v>
+        <v>130180037</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6040,34 +6040,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490647</v>
+        <v>490575</v>
       </c>
       <c r="R45" t="n">
-        <v>7023943</v>
+        <v>7023818</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6104,7 +6112,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6115,6 +6123,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6131,10 +6164,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130180037</v>
+        <v>130180060</v>
       </c>
       <c r="B46" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6142,42 +6175,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490575</v>
+        <v>490647</v>
       </c>
       <c r="R46" t="n">
-        <v>7023818</v>
+        <v>7023943</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6214,7 +6239,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6225,31 +6250,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6371,7 +6371,7 @@
         <v>130180045</v>
       </c>
       <c r="B48" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130180026</v>
+        <v>130180043</v>
       </c>
       <c r="B49" t="n">
-        <v>57741</v>
+        <v>57738</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6491,16 +6491,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6508,25 +6508,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490539</v>
+        <v>490588</v>
       </c>
       <c r="R49" t="n">
-        <v>7023926</v>
+        <v>7023887</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6563,7 +6571,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>1 individ med lockläte hördes här i skogen. En bit längre bort hördes en annan individ av spillkråka.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6580,24 +6588,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med gott om stående död ved.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6717,10 +6710,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130180043</v>
+        <v>130180067</v>
       </c>
       <c r="B51" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6728,50 +6721,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490588</v>
+        <v>490505</v>
       </c>
       <c r="R51" t="n">
-        <v>7023887</v>
+        <v>7023981</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6808,7 +6785,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>1 individ med lockläte hördes här i skogen. En bit längre bort hördes en annan individ av spillkråka.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6819,16 +6796,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med gott om stående död ved.</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6845,10 +6812,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130180067</v>
+        <v>130180026</v>
       </c>
       <c r="B52" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6856,34 +6823,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490505</v>
+        <v>490539</v>
       </c>
       <c r="R52" t="n">
-        <v>7023981</v>
+        <v>7023926</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6920,7 +6895,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6931,6 +6906,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7082,38 +7082,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130180044</v>
+        <v>130180024</v>
       </c>
       <c r="B54" t="n">
-        <v>97702</v>
+        <v>57741</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7121,10 +7125,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490663</v>
+        <v>490550</v>
       </c>
       <c r="R54" t="n">
-        <v>7024019</v>
+        <v>7023952</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7161,7 +7165,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid körspår.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7170,13 +7174,32 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7194,42 +7217,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130180024</v>
+        <v>130180044</v>
       </c>
       <c r="B55" t="n">
-        <v>57741</v>
+        <v>97704</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7237,10 +7256,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490550</v>
+        <v>490663</v>
       </c>
       <c r="R55" t="n">
-        <v>7023952</v>
+        <v>7024019</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7277,7 +7296,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid körspår.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7286,32 +7305,13 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130180015</v>
+        <v>130180052</v>
       </c>
       <c r="B56" t="n">
-        <v>57741</v>
+        <v>91661</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7340,29 +7340,24 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7372,10 +7367,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490474</v>
+        <v>490615</v>
       </c>
       <c r="R56" t="n">
-        <v>7024009</v>
+        <v>7023767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7412,7 +7407,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I stubbe och låga av knäckt gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7421,6 +7416,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7441,12 +7437,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7464,10 +7460,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130180052</v>
+        <v>130180015</v>
       </c>
       <c r="B57" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7475,24 +7471,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7502,10 +7503,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490615</v>
+        <v>490474</v>
       </c>
       <c r="R57" t="n">
-        <v>7023767</v>
+        <v>7024009</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7542,7 +7543,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>I stubbe och låga av knäckt gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7551,7 +7552,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
         <v>130180040</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>130180073</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>130180041</v>
       </c>
       <c r="B5" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>130180017</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130180039</v>
+        <v>130180074</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,54 +1284,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490650</v>
+        <v>490581</v>
       </c>
       <c r="R7" t="n">
-        <v>7023840</v>
+        <v>7023945</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1348,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,36 +1359,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1425,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130180074</v>
+        <v>130180039</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,34 +1386,54 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490581</v>
+        <v>490650</v>
       </c>
       <c r="R8" t="n">
-        <v>7023945</v>
+        <v>7023840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,6 +1481,36 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130180071</v>
+        <v>130180021</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,34 +1538,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490541</v>
+        <v>490508</v>
       </c>
       <c r="R9" t="n">
-        <v>7023902</v>
+        <v>7023972</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1610,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en hyfsst grov gran en bit innanför en hyggeskant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,6 +1621,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1629,10 +1662,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130180021</v>
+        <v>130180071</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,42 +1673,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490508</v>
+        <v>490541</v>
       </c>
       <c r="R10" t="n">
-        <v>7023972</v>
+        <v>7023902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1737,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en hyfsst grov gran en bit innanför en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,31 +1748,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1767,7 +1767,7 @@
         <v>130180070</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>130180064</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>130180028</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130180018</v>
+        <v>130180061</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,31 +2143,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2175,10 +2170,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490478</v>
+        <v>490539</v>
       </c>
       <c r="R14" t="n">
-        <v>7024001</v>
+        <v>7024036</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2215,7 +2210,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,6 +2219,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2244,12 +2240,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2267,38 +2263,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130180047</v>
+        <v>130180019</v>
       </c>
       <c r="B15" t="n">
-        <v>97704</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490586</v>
+        <v>490488</v>
       </c>
       <c r="R15" t="n">
-        <v>7023926</v>
+        <v>7023990</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2355,13 +2355,32 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2379,10 +2398,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130180061</v>
+        <v>130180018</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,26 +2409,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2417,10 +2441,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490539</v>
+        <v>490478</v>
       </c>
       <c r="R16" t="n">
-        <v>7024036</v>
+        <v>7024001</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2457,7 +2481,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2466,7 +2490,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2487,12 +2510,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2510,42 +2533,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130180019</v>
+        <v>130180047</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>97791</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2553,10 +2572,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490488</v>
+        <v>490586</v>
       </c>
       <c r="R17" t="n">
-        <v>7023990</v>
+        <v>7023926</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2593,7 +2612,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2602,32 +2621,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2648,7 +2648,7 @@
         <v>130180038</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>130180023</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>130180022</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130180020</v>
+        <v>130180051</v>
       </c>
       <c r="B21" t="n">
-        <v>57741</v>
+        <v>91748</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3070,46 +3070,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490494</v>
+        <v>490648</v>
       </c>
       <c r="R21" t="n">
-        <v>7023983</v>
+        <v>7023846</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3146,7 +3137,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3155,6 +3146,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3163,6 +3155,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3175,12 +3172,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3198,10 +3195,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180014</v>
+        <v>130180020</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3231,20 +3228,24 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490533</v>
+        <v>490494</v>
       </c>
       <c r="R22" t="n">
-        <v>7024027</v>
+        <v>7023983</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3281,7 +3282,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
+          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3333,10 +3334,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130180051</v>
+        <v>130180078</v>
       </c>
       <c r="B23" t="n">
-        <v>91661</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3344,37 +3345,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490648</v>
+        <v>490660</v>
       </c>
       <c r="R23" t="n">
-        <v>7023846</v>
+        <v>7023791</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3411,7 +3409,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3420,39 +3418,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3469,10 +3436,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130180078</v>
+        <v>130180014</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3480,34 +3447,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490660</v>
+        <v>490533</v>
       </c>
       <c r="R24" t="n">
-        <v>7023791</v>
+        <v>7024027</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3544,7 +3519,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3555,6 +3530,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3574,7 +3574,7 @@
         <v>130180046</v>
       </c>
       <c r="B25" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>130180036</v>
       </c>
       <c r="B26" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3818,10 +3818,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130180029</v>
+        <v>130180031</v>
       </c>
       <c r="B27" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490543</v>
+        <v>490546</v>
       </c>
       <c r="R27" t="n">
-        <v>7023888</v>
+        <v>7023885</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i god mängd på en gran vid en hyggeskant. Troligen  skapade 2025.</t>
+          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3957,10 +3957,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130180031</v>
+        <v>130180029</v>
       </c>
       <c r="B28" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490546</v>
+        <v>490543</v>
       </c>
       <c r="R28" t="n">
-        <v>7023885</v>
+        <v>7023888</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, i god mängd på en gran vid en hyggeskant. Troligen  skapade 2025.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4099,7 +4099,7 @@
         <v>130180009</v>
       </c>
       <c r="B29" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>130180008</v>
       </c>
       <c r="B30" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4366,52 +4366,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130180042</v>
+        <v>130180069</v>
       </c>
       <c r="B31" t="n">
-        <v>80229</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490679</v>
+        <v>490566</v>
       </c>
       <c r="R31" t="n">
-        <v>7023796</v>
+        <v>7023937</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4448,7 +4441,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4457,34 +4450,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4501,10 +4468,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180069</v>
+        <v>130180072</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4536,10 +4503,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490566</v>
+        <v>490590</v>
       </c>
       <c r="R32" t="n">
-        <v>7023937</v>
+        <v>7023801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4576,7 +4543,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4603,45 +4570,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130180072</v>
+        <v>130180042</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>80314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490590</v>
+        <v>490679</v>
       </c>
       <c r="R33" t="n">
-        <v>7023801</v>
+        <v>7023796</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4678,7 +4652,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4687,8 +4661,34 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4708,7 +4708,7 @@
         <v>130180033</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130180065</v>
+        <v>130180016</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4851,34 +4851,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490576</v>
+        <v>490471</v>
       </c>
       <c r="R35" t="n">
-        <v>7023998</v>
+        <v>7024008</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4915,7 +4923,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4926,6 +4934,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4942,10 +4975,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130180059</v>
+        <v>130180025</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4953,34 +4986,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490614</v>
+        <v>490547</v>
       </c>
       <c r="R36" t="n">
-        <v>7023878</v>
+        <v>7023930</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5017,7 +5058,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5028,6 +5069,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5044,10 +5110,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130180063</v>
+        <v>130180059</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5079,10 +5145,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490561</v>
+        <v>490614</v>
       </c>
       <c r="R37" t="n">
-        <v>7023986</v>
+        <v>7023878</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5119,7 +5185,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5146,10 +5212,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130180016</v>
+        <v>130180065</v>
       </c>
       <c r="B38" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5157,42 +5223,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490471</v>
+        <v>490576</v>
       </c>
       <c r="R38" t="n">
-        <v>7024008</v>
+        <v>7023998</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5229,7 +5287,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5240,31 +5298,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5281,10 +5314,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130180025</v>
+        <v>130180063</v>
       </c>
       <c r="B39" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5292,42 +5325,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490547</v>
+        <v>490561</v>
       </c>
       <c r="R39" t="n">
-        <v>7023930</v>
+        <v>7023986</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5364,7 +5389,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5375,31 +5400,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5419,7 +5419,7 @@
         <v>130180035</v>
       </c>
       <c r="B40" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>130180034</v>
       </c>
       <c r="B41" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>130180027</v>
       </c>
       <c r="B42" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>130180068</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>130180077</v>
       </c>
       <c r="B44" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6029,10 +6029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130180037</v>
+        <v>130180060</v>
       </c>
       <c r="B45" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6040,42 +6040,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490575</v>
+        <v>490647</v>
       </c>
       <c r="R45" t="n">
-        <v>7023818</v>
+        <v>7023943</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6112,7 +6104,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6123,31 +6115,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6164,10 +6131,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130180060</v>
+        <v>130180062</v>
       </c>
       <c r="B46" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6199,10 +6166,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490647</v>
+        <v>490550</v>
       </c>
       <c r="R46" t="n">
-        <v>7023943</v>
+        <v>7023998</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6266,10 +6233,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130180062</v>
+        <v>130180037</v>
       </c>
       <c r="B47" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6277,34 +6244,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490550</v>
+        <v>490575</v>
       </c>
       <c r="R47" t="n">
-        <v>7023998</v>
+        <v>7023818</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6341,7 +6316,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6352,6 +6327,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6371,7 +6371,7 @@
         <v>130180045</v>
       </c>
       <c r="B48" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>130180043</v>
       </c>
       <c r="B49" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130180075</v>
+        <v>130180026</v>
       </c>
       <c r="B50" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6619,34 +6619,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490602</v>
+        <v>490539</v>
       </c>
       <c r="R50" t="n">
-        <v>7023937</v>
+        <v>7023926</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6683,7 +6691,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6694,6 +6702,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6710,10 +6743,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130180067</v>
+        <v>130180075</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6745,10 +6778,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490505</v>
+        <v>490602</v>
       </c>
       <c r="R51" t="n">
-        <v>7023981</v>
+        <v>7023937</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6785,7 +6818,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6812,10 +6845,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130180026</v>
+        <v>130180067</v>
       </c>
       <c r="B52" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6823,42 +6856,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490539</v>
+        <v>490505</v>
       </c>
       <c r="R52" t="n">
-        <v>7023926</v>
+        <v>7023981</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6895,7 +6920,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6906,31 +6931,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6947,10 +6947,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130180030</v>
+        <v>130180024</v>
       </c>
       <c r="B53" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490538</v>
+        <v>490550</v>
       </c>
       <c r="R53" t="n">
-        <v>7023883</v>
+        <v>7023952</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid körspår.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7082,10 +7082,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130180024</v>
+        <v>130180030</v>
       </c>
       <c r="B54" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490550</v>
+        <v>490538</v>
       </c>
       <c r="R54" t="n">
-        <v>7023952</v>
+        <v>7023883</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid körspår.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7220,7 +7220,7 @@
         <v>130180044</v>
       </c>
       <c r="B55" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7329,10 +7329,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130180052</v>
+        <v>130180015</v>
       </c>
       <c r="B56" t="n">
-        <v>91661</v>
+        <v>57826</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7340,24 +7340,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7367,10 +7372,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490615</v>
+        <v>490474</v>
       </c>
       <c r="R56" t="n">
-        <v>7023767</v>
+        <v>7024009</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7407,7 +7412,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>I stubbe och låga av knäckt gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7416,7 +7421,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7437,12 +7441,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7460,10 +7464,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130180015</v>
+        <v>130180052</v>
       </c>
       <c r="B57" t="n">
-        <v>57741</v>
+        <v>91748</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7471,29 +7475,24 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7503,10 +7502,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490474</v>
+        <v>490615</v>
       </c>
       <c r="R57" t="n">
-        <v>7024009</v>
+        <v>7023767</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7543,7 +7542,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I stubbe och låga av knäckt gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7552,6 +7551,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130180032</v>
+        <v>130180076</v>
       </c>
       <c r="B58" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7606,46 +7606,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490566</v>
+        <v>490653</v>
       </c>
       <c r="R58" t="n">
-        <v>7023832</v>
+        <v>7023898</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7682,7 +7670,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en smal gran vid en hyggeskant.</t>
+          <t>På gran intill andra hänglavar, i barrblandskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7693,31 +7681,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7734,10 +7697,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130180076</v>
+        <v>130180066</v>
       </c>
       <c r="B59" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7769,10 +7732,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490653</v>
+        <v>490497</v>
       </c>
       <c r="R59" t="n">
-        <v>7023898</v>
+        <v>7024012</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7809,7 +7772,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gran intill andra hänglavar, i barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7836,10 +7799,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130180066</v>
+        <v>130180032</v>
       </c>
       <c r="B60" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7847,34 +7810,46 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490497</v>
+        <v>490566</v>
       </c>
       <c r="R60" t="n">
-        <v>7024012</v>
+        <v>7023832</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7911,7 +7886,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en smal gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7922,6 +7897,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130180074</v>
+        <v>130180039</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,34 +1284,54 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490581</v>
+        <v>490650</v>
       </c>
       <c r="R7" t="n">
-        <v>7023945</v>
+        <v>7023840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1368,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,6 +1379,36 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1375,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130180039</v>
+        <v>130180074</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,54 +1436,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490650</v>
+        <v>490581</v>
       </c>
       <c r="R8" t="n">
-        <v>7023840</v>
+        <v>7023945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1500,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,36 +1511,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -2132,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130180061</v>
+        <v>130180019</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,26 +2143,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2170,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490539</v>
+        <v>490488</v>
       </c>
       <c r="R14" t="n">
-        <v>7024036</v>
+        <v>7023990</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2210,7 +2215,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,7 +2224,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2240,12 +2244,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2263,7 +2267,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130180019</v>
+        <v>130180018</v>
       </c>
       <c r="B15" t="n">
         <v>57826</v>
@@ -2306,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490488</v>
+        <v>490478</v>
       </c>
       <c r="R15" t="n">
-        <v>7023990</v>
+        <v>7024001</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2398,42 +2402,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130180018</v>
+        <v>130180047</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490478</v>
+        <v>490586</v>
       </c>
       <c r="R16" t="n">
-        <v>7024001</v>
+        <v>7023926</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,32 +2490,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2533,38 +2514,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130180047</v>
+        <v>130180061</v>
       </c>
       <c r="B17" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2572,10 +2552,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490586</v>
+        <v>490539</v>
       </c>
       <c r="R17" t="n">
-        <v>7023926</v>
+        <v>7024036</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2612,7 +2592,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2628,6 +2608,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130180051</v>
+        <v>130180020</v>
       </c>
       <c r="B21" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3070,37 +3070,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490648</v>
+        <v>490494</v>
       </c>
       <c r="R21" t="n">
-        <v>7023846</v>
+        <v>7023983</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3137,7 +3146,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3146,7 +3155,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3155,11 +3163,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3172,12 +3175,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3195,57 +3198,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180020</v>
+        <v>130180046</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490494</v>
+        <v>490513</v>
       </c>
       <c r="R22" t="n">
-        <v>7023983</v>
+        <v>7023984</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3282,7 +3277,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3291,32 +3286,13 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3571,38 +3547,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130180046</v>
+        <v>130180051</v>
       </c>
       <c r="B25" t="n">
-        <v>97791</v>
+        <v>91748</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3610,10 +3585,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490513</v>
+        <v>490648</v>
       </c>
       <c r="R25" t="n">
-        <v>7023984</v>
+        <v>7023846</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3650,7 +3625,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3666,6 +3641,31 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4096,10 +4096,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130180009</v>
+        <v>130180069</v>
       </c>
       <c r="B29" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,41 +4107,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490651</v>
+        <v>490566</v>
       </c>
       <c r="R29" t="n">
-        <v>7024020</v>
+        <v>7023937</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4178,7 +4171,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I en granlåga i barrblandskog.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4187,34 +4180,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4231,10 +4198,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130180008</v>
+        <v>130180072</v>
       </c>
       <c r="B30" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4242,41 +4209,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490598</v>
+        <v>490590</v>
       </c>
       <c r="R30" t="n">
-        <v>7023986</v>
+        <v>7023801</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4313,7 +4273,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>I granlåga i barrblandskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4322,34 +4282,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4366,45 +4300,52 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130180069</v>
+        <v>130180042</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>80314</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490566</v>
+        <v>490679</v>
       </c>
       <c r="R31" t="n">
-        <v>7023937</v>
+        <v>7023796</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4441,7 +4382,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4450,8 +4391,34 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4468,10 +4435,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180072</v>
+        <v>130180033</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4479,34 +4446,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490590</v>
+        <v>490591</v>
       </c>
       <c r="R32" t="n">
-        <v>7023801</v>
+        <v>7023786</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4543,7 +4518,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4554,6 +4529,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4570,39 +4570,39 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130180042</v>
+        <v>130180009</v>
       </c>
       <c r="B33" t="n">
-        <v>80314</v>
+        <v>91728</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490679</v>
+        <v>490651</v>
       </c>
       <c r="R33" t="n">
-        <v>7023796</v>
+        <v>7024020</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>I en granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4672,22 +4672,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4705,10 +4705,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130180033</v>
+        <v>130180008</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4716,29 +4716,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4748,10 +4747,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490591</v>
+        <v>490598</v>
       </c>
       <c r="R34" t="n">
-        <v>7023786</v>
+        <v>7023986</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4788,7 +4787,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4797,6 +4796,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130180039</v>
+        <v>130180074</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,54 +1284,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490650</v>
+        <v>490581</v>
       </c>
       <c r="R7" t="n">
-        <v>7023840</v>
+        <v>7023945</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1348,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,36 +1359,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1425,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130180074</v>
+        <v>130180039</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,34 +1386,54 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490581</v>
+        <v>490650</v>
       </c>
       <c r="R8" t="n">
-        <v>7023945</v>
+        <v>7023840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,6 +1481,36 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -2132,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130180019</v>
+        <v>130180061</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,31 +2143,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2175,10 +2170,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490488</v>
+        <v>490539</v>
       </c>
       <c r="R14" t="n">
-        <v>7023990</v>
+        <v>7024036</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2215,7 +2210,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,6 +2219,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2244,12 +2240,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2267,7 +2263,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130180018</v>
+        <v>130180019</v>
       </c>
       <c r="B15" t="n">
         <v>57826</v>
@@ -2310,10 +2306,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490478</v>
+        <v>490488</v>
       </c>
       <c r="R15" t="n">
-        <v>7024001</v>
+        <v>7023990</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2402,38 +2398,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130180047</v>
+        <v>130180018</v>
       </c>
       <c r="B16" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490586</v>
+        <v>490478</v>
       </c>
       <c r="R16" t="n">
-        <v>7023926</v>
+        <v>7024001</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,13 +2490,32 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2514,37 +2533,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130180061</v>
+        <v>130180047</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2552,10 +2572,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490539</v>
+        <v>490586</v>
       </c>
       <c r="R17" t="n">
-        <v>7024036</v>
+        <v>7023926</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2592,7 +2612,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2608,26 +2628,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130180038</v>
+        <v>130180023</v>
       </c>
       <c r="B18" t="n">
         <v>57826</v>
@@ -2678,24 +2678,20 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490648</v>
+        <v>490509</v>
       </c>
       <c r="R18" t="n">
-        <v>7023846</v>
+        <v>7023962</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2732,7 +2728,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gamla bohål i en stående död gran med full längd som har fruktkroppar av granticka. Ett bohål (diameter 4 cm) på 1,8 meters höjd, och ett bohål (diameter 4,5 cm) på 2,1 meters höjd. Finns även fler bohål och andra hackade hål högre upp i granstammen. Troligen bohål som tidigare använts av tretåig hackspett. Hålens storlek och att en hona av tretåig hackspett födosökte precis intill styrker detta.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2749,11 +2745,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2766,12 +2757,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2789,7 +2780,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130180023</v>
+        <v>130180022</v>
       </c>
       <c r="B19" t="n">
         <v>57826</v>
@@ -2832,10 +2823,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490509</v>
+        <v>490522</v>
       </c>
       <c r="R19" t="n">
-        <v>7023962</v>
+        <v>7023957</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2872,7 +2863,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2924,7 +2915,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130180022</v>
+        <v>130180038</v>
       </c>
       <c r="B20" t="n">
         <v>57826</v>
@@ -2957,20 +2948,24 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490522</v>
+        <v>490648</v>
       </c>
       <c r="R20" t="n">
-        <v>7023957</v>
+        <v>7023846</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3007,7 +3002,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
+          <t>Gamla bohål i en stående död gran med full längd som har fruktkroppar av granticka. Ett bohål (diameter 4 cm) på 1,8 meters höjd, och ett bohål (diameter 4,5 cm) på 2,1 meters höjd. Finns även fler bohål och andra hackade hål högre upp i granstammen. Troligen bohål som tidigare använts av tretåig hackspett. Hålens storlek och att en hona av tretåig hackspett födosökte precis intill styrker detta.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3024,6 +3019,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3036,12 +3036,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130180020</v>
+        <v>130180051</v>
       </c>
       <c r="B21" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3070,46 +3070,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490494</v>
+        <v>490648</v>
       </c>
       <c r="R21" t="n">
-        <v>7023983</v>
+        <v>7023846</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3146,7 +3137,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3155,6 +3146,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3163,6 +3155,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3175,12 +3172,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3198,49 +3195,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180046</v>
+        <v>130180020</v>
       </c>
       <c r="B22" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490513</v>
+        <v>490494</v>
       </c>
       <c r="R22" t="n">
-        <v>7023984</v>
+        <v>7023983</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3277,7 +3282,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3286,13 +3291,32 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3547,37 +3571,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130180051</v>
+        <v>130180046</v>
       </c>
       <c r="B25" t="n">
-        <v>91748</v>
+        <v>97791</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3585,10 +3610,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490648</v>
+        <v>490513</v>
       </c>
       <c r="R25" t="n">
-        <v>7023846</v>
+        <v>7023984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3625,7 +3650,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3641,31 +3666,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4096,10 +4096,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130180069</v>
+        <v>130180009</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,34 +4107,41 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490566</v>
+        <v>490651</v>
       </c>
       <c r="R29" t="n">
-        <v>7023937</v>
+        <v>7024020</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4171,7 +4178,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>I en granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4180,8 +4187,34 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4198,10 +4231,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130180072</v>
+        <v>130180008</v>
       </c>
       <c r="B30" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4209,34 +4242,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490590</v>
+        <v>490598</v>
       </c>
       <c r="R30" t="n">
-        <v>7023801</v>
+        <v>7023986</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4273,7 +4313,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>I granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4282,8 +4322,34 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4300,52 +4366,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130180042</v>
+        <v>130180069</v>
       </c>
       <c r="B31" t="n">
-        <v>80314</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490679</v>
+        <v>490566</v>
       </c>
       <c r="R31" t="n">
-        <v>7023796</v>
+        <v>7023937</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4382,7 +4441,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4391,34 +4450,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4435,10 +4468,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180033</v>
+        <v>130180072</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4446,42 +4479,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490591</v>
+        <v>490590</v>
       </c>
       <c r="R32" t="n">
-        <v>7023786</v>
+        <v>7023801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4518,7 +4543,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4529,31 +4554,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4570,39 +4570,39 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130180009</v>
+        <v>130180042</v>
       </c>
       <c r="B33" t="n">
-        <v>91728</v>
+        <v>80314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490651</v>
+        <v>490679</v>
       </c>
       <c r="R33" t="n">
-        <v>7024020</v>
+        <v>7023796</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>I en granlåga i barrblandskog.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4672,22 +4672,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4705,10 +4705,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130180008</v>
+        <v>130180033</v>
       </c>
       <c r="B34" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4716,28 +4716,29 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4747,10 +4748,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490598</v>
+        <v>490591</v>
       </c>
       <c r="R34" t="n">
-        <v>7023986</v>
+        <v>7023786</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4787,7 +4788,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>I granlåga i barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4796,7 +4797,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130180043</v>
+        <v>130180026</v>
       </c>
       <c r="B49" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6491,16 +6491,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6508,33 +6508,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490588</v>
+        <v>490539</v>
       </c>
       <c r="R49" t="n">
-        <v>7023887</v>
+        <v>7023926</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6571,7 +6563,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1 individ med lockläte hördes här i skogen. En bit längre bort hördes en annan individ av spillkråka.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6588,9 +6580,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med gott om stående död ved.</t>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6608,10 +6615,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130180026</v>
+        <v>130180075</v>
       </c>
       <c r="B50" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6619,42 +6626,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490539</v>
+        <v>490602</v>
       </c>
       <c r="R50" t="n">
-        <v>7023926</v>
+        <v>7023937</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6691,7 +6690,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6702,31 +6701,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6743,7 +6717,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130180075</v>
+        <v>130180067</v>
       </c>
       <c r="B51" t="n">
         <v>79180</v>
@@ -6778,10 +6752,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490602</v>
+        <v>490505</v>
       </c>
       <c r="R51" t="n">
-        <v>7023937</v>
+        <v>7023981</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6818,7 +6792,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6845,10 +6819,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130180067</v>
+        <v>130180043</v>
       </c>
       <c r="B52" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6856,34 +6830,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490505</v>
+        <v>490588</v>
       </c>
       <c r="R52" t="n">
-        <v>7023981</v>
+        <v>7023887</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6920,7 +6910,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>1 individ med lockläte hördes här i skogen. En bit längre bort hördes en annan individ av spillkråka.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6931,6 +6921,16 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med gott om stående död ved.</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7595,7 +7595,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130180076</v>
+        <v>130180066</v>
       </c>
       <c r="B58" t="n">
         <v>79180</v>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490653</v>
+        <v>490497</v>
       </c>
       <c r="R58" t="n">
-        <v>7023898</v>
+        <v>7024012</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gran intill andra hänglavar, i barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7697,7 +7697,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130180066</v>
+        <v>130180076</v>
       </c>
       <c r="B59" t="n">
         <v>79180</v>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490497</v>
+        <v>490653</v>
       </c>
       <c r="R59" t="n">
-        <v>7024012</v>
+        <v>7023898</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran intill andra hänglavar, i barrblandskog.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130180041</v>
+        <v>130180017</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,50 +1021,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490626</v>
+        <v>490478</v>
       </c>
       <c r="R5" t="n">
-        <v>7023887</v>
+        <v>7024005</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 1 individ, ev. fler. Fyndplatsen finns i flerskiktad äldre barrblandskog.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,9 +1110,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre barrblandskog.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1138,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130180017</v>
+        <v>130180041</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,42 +1156,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490478</v>
+        <v>490626</v>
       </c>
       <c r="R6" t="n">
-        <v>7024005</v>
+        <v>7023887</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1236,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 1 individ, ev. fler. Fyndplatsen finns i flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,24 +1253,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130180074</v>
+        <v>130180039</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,34 +1284,54 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490581</v>
+        <v>490650</v>
       </c>
       <c r="R7" t="n">
-        <v>7023945</v>
+        <v>7023840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1368,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,6 +1379,36 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1375,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130180039</v>
+        <v>130180074</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,54 +1436,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490650</v>
+        <v>490581</v>
       </c>
       <c r="R8" t="n">
-        <v>7023840</v>
+        <v>7023945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1500,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,36 +1511,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130180021</v>
+        <v>130180071</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,42 +1538,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490508</v>
+        <v>490541</v>
       </c>
       <c r="R9" t="n">
-        <v>7023972</v>
+        <v>7023902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1610,7 +1602,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en hyfsst grov gran en bit innanför en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,31 +1613,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1662,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130180071</v>
+        <v>130180021</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,34 +1640,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490541</v>
+        <v>490508</v>
       </c>
       <c r="R10" t="n">
-        <v>7023902</v>
+        <v>7023972</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1737,7 +1712,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en hyfsst grov gran en bit innanför en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,6 +1723,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1764,7 +1764,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130180070</v>
+        <v>130180064</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1793,19 +1793,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490547</v>
+        <v>490655</v>
       </c>
       <c r="R11" t="n">
-        <v>7023925</v>
+        <v>7024022</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,7 +1839,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,34 +1848,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1895,7 +1866,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130180064</v>
+        <v>130180070</v>
       </c>
       <c r="B12" t="n">
         <v>79180</v>
@@ -1924,16 +1895,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490655</v>
+        <v>490547</v>
       </c>
       <c r="R12" t="n">
-        <v>7024022</v>
+        <v>7023925</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1970,7 +1944,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,8 +1953,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2645,7 +2645,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130180023</v>
+        <v>130180022</v>
       </c>
       <c r="B18" t="n">
         <v>57826</v>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490509</v>
+        <v>490522</v>
       </c>
       <c r="R18" t="n">
-        <v>7023962</v>
+        <v>7023957</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2780,7 +2780,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130180022</v>
+        <v>130180023</v>
       </c>
       <c r="B19" t="n">
         <v>57826</v>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490522</v>
+        <v>490509</v>
       </c>
       <c r="R19" t="n">
-        <v>7023957</v>
+        <v>7023962</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3059,10 +3059,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130180051</v>
+        <v>130180078</v>
       </c>
       <c r="B21" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3070,37 +3070,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490648</v>
+        <v>490660</v>
       </c>
       <c r="R21" t="n">
-        <v>7023846</v>
+        <v>7023791</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3137,7 +3134,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3146,39 +3143,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3195,10 +3161,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180020</v>
+        <v>130180051</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3206,46 +3172,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490494</v>
+        <v>490648</v>
       </c>
       <c r="R22" t="n">
-        <v>7023983</v>
+        <v>7023846</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3282,7 +3239,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3291,6 +3248,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3299,6 +3257,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3311,12 +3274,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3334,10 +3297,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130180078</v>
+        <v>130180020</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3345,34 +3308,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490660</v>
+        <v>490494</v>
       </c>
       <c r="R23" t="n">
-        <v>7023791</v>
+        <v>7023983</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3409,7 +3384,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3420,6 +3395,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3683,7 +3683,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130180036</v>
+        <v>130180031</v>
       </c>
       <c r="B26" t="n">
         <v>57826</v>
@@ -3719,17 +3719,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490589</v>
+        <v>490546</v>
       </c>
       <c r="R26" t="n">
-        <v>7023793</v>
+        <v>7023885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3766,7 +3770,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3780,7 +3784,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3818,7 +3822,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130180031</v>
+        <v>130180036</v>
       </c>
       <c r="B27" t="n">
         <v>57826</v>
@@ -3854,21 +3858,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490546</v>
+        <v>490589</v>
       </c>
       <c r="R27" t="n">
-        <v>7023885</v>
+        <v>7023793</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4096,10 +4096,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130180009</v>
+        <v>130180033</v>
       </c>
       <c r="B29" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,28 +4107,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4138,10 +4139,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490651</v>
+        <v>490591</v>
       </c>
       <c r="R29" t="n">
-        <v>7024020</v>
+        <v>7023786</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4178,7 +4179,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I en granlåga i barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4187,7 +4188,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4208,12 +4208,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130180008</v>
+        <v>130180069</v>
       </c>
       <c r="B30" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4242,41 +4242,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490598</v>
+        <v>490566</v>
       </c>
       <c r="R30" t="n">
-        <v>7023986</v>
+        <v>7023937</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4313,7 +4306,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>I granlåga i barrblandskog.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4322,34 +4315,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4366,7 +4333,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130180069</v>
+        <v>130180072</v>
       </c>
       <c r="B31" t="n">
         <v>79180</v>
@@ -4401,10 +4368,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490566</v>
+        <v>490590</v>
       </c>
       <c r="R31" t="n">
-        <v>7023937</v>
+        <v>7023801</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4441,7 +4408,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4468,45 +4435,52 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180072</v>
+        <v>130180042</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>80314</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490590</v>
+        <v>490679</v>
       </c>
       <c r="R32" t="n">
-        <v>7023801</v>
+        <v>7023796</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4543,7 +4517,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4552,8 +4526,34 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4570,39 +4570,39 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130180042</v>
+        <v>130180009</v>
       </c>
       <c r="B33" t="n">
-        <v>80314</v>
+        <v>91728</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490679</v>
+        <v>490651</v>
       </c>
       <c r="R33" t="n">
-        <v>7023796</v>
+        <v>7024020</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>I en granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4672,22 +4672,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4705,10 +4705,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130180033</v>
+        <v>130180008</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4716,29 +4716,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4748,10 +4747,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490591</v>
+        <v>490598</v>
       </c>
       <c r="R34" t="n">
-        <v>7023786</v>
+        <v>7023986</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4788,7 +4787,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4797,6 +4796,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130180016</v>
+        <v>130180065</v>
       </c>
       <c r="B35" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4851,42 +4851,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490471</v>
+        <v>490576</v>
       </c>
       <c r="R35" t="n">
-        <v>7024008</v>
+        <v>7023998</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4923,7 +4915,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4934,31 +4926,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4975,10 +4942,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130180025</v>
+        <v>130180059</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4986,42 +4953,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490547</v>
+        <v>490614</v>
       </c>
       <c r="R36" t="n">
-        <v>7023930</v>
+        <v>7023878</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5058,7 +5017,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5069,31 +5028,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5110,7 +5044,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130180059</v>
+        <v>130180063</v>
       </c>
       <c r="B37" t="n">
         <v>79180</v>
@@ -5145,10 +5079,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490614</v>
+        <v>490561</v>
       </c>
       <c r="R37" t="n">
-        <v>7023878</v>
+        <v>7023986</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5185,7 +5119,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5212,10 +5146,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130180065</v>
+        <v>130180035</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5223,34 +5157,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490576</v>
+        <v>490603</v>
       </c>
       <c r="R38" t="n">
-        <v>7023998</v>
+        <v>7023797</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5287,7 +5229,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5298,6 +5240,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5314,10 +5281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130180063</v>
+        <v>130180034</v>
       </c>
       <c r="B39" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5325,34 +5292,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490561</v>
+        <v>490609</v>
       </c>
       <c r="R39" t="n">
-        <v>7023986</v>
+        <v>7023788</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5389,7 +5364,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5400,6 +5375,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5416,7 +5416,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130180035</v>
+        <v>130180027</v>
       </c>
       <c r="B40" t="n">
         <v>57826</v>
@@ -5452,17 +5452,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490603</v>
+        <v>490539</v>
       </c>
       <c r="R40" t="n">
-        <v>7023797</v>
+        <v>7023923</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5499,7 +5503,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
+          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5551,7 +5555,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130180034</v>
+        <v>130180016</v>
       </c>
       <c r="B41" t="n">
         <v>57826</v>
@@ -5594,10 +5598,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490609</v>
+        <v>490471</v>
       </c>
       <c r="R41" t="n">
-        <v>7023788</v>
+        <v>7024008</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5634,7 +5638,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5648,7 +5652,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5686,7 +5690,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130180027</v>
+        <v>130180025</v>
       </c>
       <c r="B42" t="n">
         <v>57826</v>
@@ -5722,21 +5726,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490539</v>
+        <v>490547</v>
       </c>
       <c r="R42" t="n">
-        <v>7023923</v>
+        <v>7023930</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6029,10 +6029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130180060</v>
+        <v>130180037</v>
       </c>
       <c r="B45" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6040,34 +6040,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490647</v>
+        <v>490575</v>
       </c>
       <c r="R45" t="n">
-        <v>7023943</v>
+        <v>7023818</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6104,7 +6112,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6115,6 +6123,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6131,7 +6164,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130180062</v>
+        <v>130180060</v>
       </c>
       <c r="B46" t="n">
         <v>79180</v>
@@ -6166,10 +6199,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490550</v>
+        <v>490647</v>
       </c>
       <c r="R46" t="n">
-        <v>7023998</v>
+        <v>7023943</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6233,10 +6266,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130180037</v>
+        <v>130180062</v>
       </c>
       <c r="B47" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,42 +6277,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490575</v>
+        <v>490550</v>
       </c>
       <c r="R47" t="n">
-        <v>7023818</v>
+        <v>7023998</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6316,7 +6341,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6327,31 +6352,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6480,10 +6480,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130180026</v>
+        <v>130180075</v>
       </c>
       <c r="B49" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6491,42 +6491,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490539</v>
+        <v>490602</v>
       </c>
       <c r="R49" t="n">
-        <v>7023926</v>
+        <v>7023937</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6563,7 +6555,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6574,31 +6566,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6615,7 +6582,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130180075</v>
+        <v>130180067</v>
       </c>
       <c r="B50" t="n">
         <v>79180</v>
@@ -6650,10 +6617,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490602</v>
+        <v>490505</v>
       </c>
       <c r="R50" t="n">
-        <v>7023937</v>
+        <v>7023981</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6690,7 +6657,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6717,10 +6684,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130180067</v>
+        <v>130180043</v>
       </c>
       <c r="B51" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6728,34 +6695,50 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490505</v>
+        <v>490588</v>
       </c>
       <c r="R51" t="n">
-        <v>7023981</v>
+        <v>7023887</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6792,7 +6775,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>1 individ med lockläte hördes här i skogen. En bit längre bort hördes en annan individ av spillkråka.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6803,6 +6786,16 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med gott om stående död ved.</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6819,10 +6812,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130180043</v>
+        <v>130180026</v>
       </c>
       <c r="B52" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6830,16 +6823,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6847,33 +6840,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490588</v>
+        <v>490539</v>
       </c>
       <c r="R52" t="n">
-        <v>7023887</v>
+        <v>7023926</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6910,7 +6895,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>1 individ med lockläte hördes här i skogen. En bit längre bort hördes en annan individ av spillkråka.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6927,9 +6912,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med gott om stående död ved.</t>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6947,7 +6947,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130180024</v>
+        <v>130180030</v>
       </c>
       <c r="B53" t="n">
         <v>57826</v>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490550</v>
+        <v>490538</v>
       </c>
       <c r="R53" t="n">
-        <v>7023952</v>
+        <v>7023883</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid körspår.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7082,7 +7082,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130180030</v>
+        <v>130180024</v>
       </c>
       <c r="B54" t="n">
         <v>57826</v>
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490538</v>
+        <v>490550</v>
       </c>
       <c r="R54" t="n">
-        <v>7023883</v>
+        <v>7023952</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid körspår.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130180039</v>
+        <v>130180074</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,54 +1284,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490650</v>
+        <v>490581</v>
       </c>
       <c r="R7" t="n">
-        <v>7023840</v>
+        <v>7023945</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1348,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,36 +1359,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1425,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130180074</v>
+        <v>130180039</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,34 +1386,54 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490581</v>
+        <v>490650</v>
       </c>
       <c r="R8" t="n">
-        <v>7023945</v>
+        <v>7023840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,6 +1481,36 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1764,7 +1764,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130180064</v>
+        <v>130180070</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1793,16 +1793,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490655</v>
+        <v>490547</v>
       </c>
       <c r="R11" t="n">
-        <v>7024022</v>
+        <v>7023925</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1839,7 +1842,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,8 +1851,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1866,7 +1895,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130180070</v>
+        <v>130180064</v>
       </c>
       <c r="B12" t="n">
         <v>79180</v>
@@ -1895,19 +1924,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490547</v>
+        <v>490655</v>
       </c>
       <c r="R12" t="n">
-        <v>7023925</v>
+        <v>7024022</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1944,7 +1970,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1953,34 +1979,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2132,37 +2132,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130180061</v>
+        <v>130180047</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2170,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490539</v>
+        <v>490586</v>
       </c>
       <c r="R14" t="n">
-        <v>7024036</v>
+        <v>7023926</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2210,7 +2211,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2226,26 +2227,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2263,10 +2244,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130180019</v>
+        <v>130180061</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2274,31 +2255,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2306,10 +2282,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490488</v>
+        <v>490539</v>
       </c>
       <c r="R15" t="n">
-        <v>7023990</v>
+        <v>7024036</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2322,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2355,6 +2331,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2375,12 +2352,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2398,7 +2375,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130180018</v>
+        <v>130180019</v>
       </c>
       <c r="B16" t="n">
         <v>57826</v>
@@ -2441,10 +2418,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490478</v>
+        <v>490488</v>
       </c>
       <c r="R16" t="n">
-        <v>7024001</v>
+        <v>7023990</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2533,38 +2510,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130180047</v>
+        <v>130180018</v>
       </c>
       <c r="B17" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2572,10 +2553,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490586</v>
+        <v>490478</v>
       </c>
       <c r="R17" t="n">
-        <v>7023926</v>
+        <v>7024001</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2612,7 +2593,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2621,13 +2602,32 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130180022</v>
+        <v>130180038</v>
       </c>
       <c r="B18" t="n">
         <v>57826</v>
@@ -2678,20 +2678,24 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490522</v>
+        <v>490648</v>
       </c>
       <c r="R18" t="n">
-        <v>7023957</v>
+        <v>7023846</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2728,7 +2732,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
+          <t>Gamla bohål i en stående död gran med full längd som har fruktkroppar av granticka. Ett bohål (diameter 4 cm) på 1,8 meters höjd, och ett bohål (diameter 4,5 cm) på 2,1 meters höjd. Finns även fler bohål och andra hackade hål högre upp i granstammen. Troligen bohål som tidigare använts av tretåig hackspett. Hålens storlek och att en hona av tretåig hackspett födosökte precis intill styrker detta.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2745,6 +2749,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2757,12 +2766,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2915,7 +2924,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130180038</v>
+        <v>130180022</v>
       </c>
       <c r="B20" t="n">
         <v>57826</v>
@@ -2948,24 +2957,20 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490648</v>
+        <v>490522</v>
       </c>
       <c r="R20" t="n">
-        <v>7023846</v>
+        <v>7023957</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3002,7 +3007,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gamla bohål i en stående död gran med full längd som har fruktkroppar av granticka. Ett bohål (diameter 4 cm) på 1,8 meters höjd, och ett bohål (diameter 4,5 cm) på 2,1 meters höjd. Finns även fler bohål och andra hackade hål högre upp i granstammen. Troligen bohål som tidigare använts av tretåig hackspett. Hålens storlek och att en hona av tretåig hackspett födosökte precis intill styrker detta.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3019,11 +3024,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3036,12 +3036,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180051</v>
+        <v>130180020</v>
       </c>
       <c r="B22" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3172,37 +3172,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490648</v>
+        <v>490494</v>
       </c>
       <c r="R22" t="n">
-        <v>7023846</v>
+        <v>7023983</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3239,7 +3248,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3248,7 +3257,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3257,11 +3265,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3274,12 +3277,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3297,7 +3300,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130180020</v>
+        <v>130180014</v>
       </c>
       <c r="B23" t="n">
         <v>57826</v>
@@ -3330,24 +3333,20 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490494</v>
+        <v>490533</v>
       </c>
       <c r="R23" t="n">
-        <v>7023983</v>
+        <v>7024027</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3384,7 +3383,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
+          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3436,42 +3435,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130180014</v>
+        <v>130180046</v>
       </c>
       <c r="B24" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3479,10 +3474,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490533</v>
+        <v>490513</v>
       </c>
       <c r="R24" t="n">
-        <v>7024027</v>
+        <v>7023984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3519,7 +3514,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3528,32 +3523,13 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3571,38 +3547,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130180046</v>
+        <v>130180051</v>
       </c>
       <c r="B25" t="n">
-        <v>97791</v>
+        <v>91748</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3610,10 +3585,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490513</v>
+        <v>490648</v>
       </c>
       <c r="R25" t="n">
-        <v>7023984</v>
+        <v>7023846</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3650,7 +3625,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3666,6 +3641,31 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130180031</v>
+        <v>130180036</v>
       </c>
       <c r="B26" t="n">
         <v>57826</v>
@@ -3719,21 +3719,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490546</v>
+        <v>490589</v>
       </c>
       <c r="R26" t="n">
-        <v>7023885</v>
+        <v>7023793</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3770,7 +3766,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3784,7 +3780,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3822,7 +3818,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130180036</v>
+        <v>130180031</v>
       </c>
       <c r="B27" t="n">
         <v>57826</v>
@@ -3858,17 +3854,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490589</v>
+        <v>490546</v>
       </c>
       <c r="R27" t="n">
-        <v>7023793</v>
+        <v>7023885</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4096,10 +4096,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130180033</v>
+        <v>130180009</v>
       </c>
       <c r="B29" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,29 +4107,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4139,10 +4138,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490591</v>
+        <v>490651</v>
       </c>
       <c r="R29" t="n">
-        <v>7023786</v>
+        <v>7024020</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4179,7 +4178,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I en granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4188,6 +4187,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4208,12 +4208,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130180069</v>
+        <v>130180008</v>
       </c>
       <c r="B30" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4242,34 +4242,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490566</v>
+        <v>490598</v>
       </c>
       <c r="R30" t="n">
-        <v>7023937</v>
+        <v>7023986</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4306,7 +4313,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>I granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4315,8 +4322,34 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4435,39 +4468,40 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180042</v>
+        <v>130180033</v>
       </c>
       <c r="B32" t="n">
-        <v>80314</v>
+        <v>57826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4477,10 +4511,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490679</v>
+        <v>490591</v>
       </c>
       <c r="R32" t="n">
-        <v>7023796</v>
+        <v>7023786</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4517,7 +4551,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4526,7 +4560,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4537,22 +4570,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4570,10 +4603,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130180009</v>
+        <v>130180069</v>
       </c>
       <c r="B33" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4581,41 +4614,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490651</v>
+        <v>490566</v>
       </c>
       <c r="R33" t="n">
-        <v>7024020</v>
+        <v>7023937</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4652,7 +4678,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>I en granlåga i barrblandskog.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4661,34 +4687,8 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4705,39 +4705,39 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130180008</v>
+        <v>130180042</v>
       </c>
       <c r="B34" t="n">
-        <v>91728</v>
+        <v>80314</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490598</v>
+        <v>490679</v>
       </c>
       <c r="R34" t="n">
-        <v>7023986</v>
+        <v>7023796</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>I granlåga i barrblandskog.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4807,22 +4807,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4942,7 +4942,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130180059</v>
+        <v>130180063</v>
       </c>
       <c r="B36" t="n">
         <v>79180</v>
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490614</v>
+        <v>490561</v>
       </c>
       <c r="R36" t="n">
-        <v>7023878</v>
+        <v>7023986</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5044,7 +5044,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130180063</v>
+        <v>130180059</v>
       </c>
       <c r="B37" t="n">
         <v>79180</v>
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490561</v>
+        <v>490614</v>
       </c>
       <c r="R37" t="n">
-        <v>7023986</v>
+        <v>7023878</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5146,7 +5146,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130180035</v>
+        <v>130180016</v>
       </c>
       <c r="B38" t="n">
         <v>57826</v>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490603</v>
+        <v>490471</v>
       </c>
       <c r="R38" t="n">
-        <v>7023797</v>
+        <v>7024008</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
+          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5281,7 +5281,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130180034</v>
+        <v>130180025</v>
       </c>
       <c r="B39" t="n">
         <v>57826</v>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490609</v>
+        <v>490547</v>
       </c>
       <c r="R39" t="n">
-        <v>7023788</v>
+        <v>7023930</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5416,7 +5416,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130180027</v>
+        <v>130180035</v>
       </c>
       <c r="B40" t="n">
         <v>57826</v>
@@ -5452,21 +5452,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490539</v>
+        <v>490603</v>
       </c>
       <c r="R40" t="n">
-        <v>7023923</v>
+        <v>7023797</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5503,7 +5499,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
+          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5555,7 +5551,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130180016</v>
+        <v>130180034</v>
       </c>
       <c r="B41" t="n">
         <v>57826</v>
@@ -5598,10 +5594,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490471</v>
+        <v>490609</v>
       </c>
       <c r="R41" t="n">
-        <v>7024008</v>
+        <v>7023788</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5638,7 +5634,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5652,7 +5648,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5690,7 +5686,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130180025</v>
+        <v>130180027</v>
       </c>
       <c r="B42" t="n">
         <v>57826</v>
@@ -5726,17 +5722,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490547</v>
+        <v>490539</v>
       </c>
       <c r="R42" t="n">
-        <v>7023930</v>
+        <v>7023923</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6164,7 +6164,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130180060</v>
+        <v>130180062</v>
       </c>
       <c r="B46" t="n">
         <v>79180</v>
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490647</v>
+        <v>490550</v>
       </c>
       <c r="R46" t="n">
-        <v>7023943</v>
+        <v>7023998</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6266,7 +6266,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130180062</v>
+        <v>130180060</v>
       </c>
       <c r="B47" t="n">
         <v>79180</v>
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490550</v>
+        <v>490647</v>
       </c>
       <c r="R47" t="n">
-        <v>7023998</v>
+        <v>7023943</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6582,10 +6582,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130180067</v>
+        <v>130180043</v>
       </c>
       <c r="B50" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6593,34 +6593,50 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490505</v>
+        <v>490588</v>
       </c>
       <c r="R50" t="n">
-        <v>7023981</v>
+        <v>7023887</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6657,7 +6673,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>1 individ med lockläte hördes här i skogen. En bit längre bort hördes en annan individ av spillkråka.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6668,6 +6684,16 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med gott om stående död ved.</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6684,10 +6710,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130180043</v>
+        <v>130180026</v>
       </c>
       <c r="B51" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6695,16 +6721,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6712,33 +6738,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490588</v>
+        <v>490539</v>
       </c>
       <c r="R51" t="n">
-        <v>7023887</v>
+        <v>7023926</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6775,7 +6793,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>1 individ med lockläte hördes här i skogen. En bit längre bort hördes en annan individ av spillkråka.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6792,9 +6810,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med gott om stående död ved.</t>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6812,10 +6845,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130180026</v>
+        <v>130180067</v>
       </c>
       <c r="B52" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6823,42 +6856,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490539</v>
+        <v>490505</v>
       </c>
       <c r="R52" t="n">
-        <v>7023926</v>
+        <v>7023981</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6895,7 +6920,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6906,31 +6931,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130180015</v>
+        <v>130180052</v>
       </c>
       <c r="B56" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7340,29 +7340,24 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7372,10 +7367,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490474</v>
+        <v>490615</v>
       </c>
       <c r="R56" t="n">
-        <v>7024009</v>
+        <v>7023767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7412,7 +7407,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I stubbe och låga av knäckt gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7421,6 +7416,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7441,12 +7437,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7464,10 +7460,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130180052</v>
+        <v>130180015</v>
       </c>
       <c r="B57" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7475,24 +7471,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7502,10 +7503,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490615</v>
+        <v>490474</v>
       </c>
       <c r="R57" t="n">
-        <v>7023767</v>
+        <v>7024009</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7542,7 +7543,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>I stubbe och låga av knäckt gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7551,7 +7552,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7595,7 +7595,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130180066</v>
+        <v>130180076</v>
       </c>
       <c r="B58" t="n">
         <v>79180</v>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490497</v>
+        <v>490653</v>
       </c>
       <c r="R58" t="n">
-        <v>7024012</v>
+        <v>7023898</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran intill andra hänglavar, i barrblandskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7697,7 +7697,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130180076</v>
+        <v>130180066</v>
       </c>
       <c r="B59" t="n">
         <v>79180</v>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490653</v>
+        <v>490497</v>
       </c>
       <c r="R59" t="n">
-        <v>7023898</v>
+        <v>7024012</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gran intill andra hänglavar, i barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -1527,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130180071</v>
+        <v>130180021</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,34 +1538,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490541</v>
+        <v>490508</v>
       </c>
       <c r="R9" t="n">
-        <v>7023902</v>
+        <v>7023972</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1610,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en hyfsst grov gran en bit innanför en hyggeskant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,6 +1621,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1629,10 +1662,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130180021</v>
+        <v>130180071</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,42 +1673,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490508</v>
+        <v>490541</v>
       </c>
       <c r="R10" t="n">
-        <v>7023972</v>
+        <v>7023902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1737,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en hyfsst grov gran en bit innanför en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,31 +1748,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -2132,38 +2132,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130180047</v>
+        <v>130180019</v>
       </c>
       <c r="B14" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2171,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490586</v>
+        <v>490488</v>
       </c>
       <c r="R14" t="n">
-        <v>7023926</v>
+        <v>7023990</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2211,7 +2215,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,13 +2224,32 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2244,10 +2267,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130180061</v>
+        <v>130180018</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,26 +2278,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2282,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490539</v>
+        <v>490478</v>
       </c>
       <c r="R15" t="n">
-        <v>7024036</v>
+        <v>7024001</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2322,7 +2350,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,7 +2359,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2352,12 +2379,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2375,10 +2402,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130180019</v>
+        <v>130180061</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,31 +2413,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2418,10 +2440,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490488</v>
+        <v>490539</v>
       </c>
       <c r="R16" t="n">
-        <v>7023990</v>
+        <v>7024036</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2458,7 +2480,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2467,6 +2489,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2487,12 +2510,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2510,42 +2533,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130180018</v>
+        <v>130180047</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2553,10 +2572,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490478</v>
+        <v>490586</v>
       </c>
       <c r="R17" t="n">
-        <v>7024001</v>
+        <v>7023926</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2593,7 +2612,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2602,32 +2621,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2739,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
@@ -3161,57 +3161,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180020</v>
+        <v>130180046</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490494</v>
+        <v>490513</v>
       </c>
       <c r="R22" t="n">
-        <v>7023983</v>
+        <v>7023984</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3248,7 +3240,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3257,32 +3249,13 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3300,10 +3273,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130180014</v>
+        <v>130180051</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3311,29 +3284,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3343,10 +3311,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490533</v>
+        <v>490648</v>
       </c>
       <c r="R23" t="n">
-        <v>7024027</v>
+        <v>7023846</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3383,7 +3351,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3392,6 +3360,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3400,6 +3369,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3412,12 +3386,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3435,49 +3409,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130180046</v>
+        <v>130180020</v>
       </c>
       <c r="B24" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490513</v>
+        <v>490494</v>
       </c>
       <c r="R24" t="n">
-        <v>7023984</v>
+        <v>7023983</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3514,7 +3496,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3523,13 +3505,32 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3547,10 +3548,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130180051</v>
+        <v>130180014</v>
       </c>
       <c r="B25" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3558,24 +3559,29 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3585,10 +3591,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490648</v>
+        <v>490533</v>
       </c>
       <c r="R25" t="n">
-        <v>7023846</v>
+        <v>7024027</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3625,7 +3631,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3634,7 +3640,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3643,11 +3648,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ25" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3660,12 +3660,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4096,10 +4096,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130180009</v>
+        <v>130180069</v>
       </c>
       <c r="B29" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,41 +4107,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490651</v>
+        <v>490566</v>
       </c>
       <c r="R29" t="n">
-        <v>7024020</v>
+        <v>7023937</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4178,7 +4171,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I en granlåga i barrblandskog.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4187,34 +4180,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4231,10 +4198,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130180008</v>
+        <v>130180072</v>
       </c>
       <c r="B30" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4242,41 +4209,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490598</v>
+        <v>490590</v>
       </c>
       <c r="R30" t="n">
-        <v>7023986</v>
+        <v>7023801</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4313,7 +4273,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>I granlåga i barrblandskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4322,34 +4282,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4366,10 +4300,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130180072</v>
+        <v>130180009</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4377,34 +4311,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490590</v>
+        <v>490651</v>
       </c>
       <c r="R31" t="n">
-        <v>7023801</v>
+        <v>7024020</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4441,7 +4382,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>I en granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4450,8 +4391,34 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4468,10 +4435,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180033</v>
+        <v>130180008</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4479,29 +4446,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4511,10 +4477,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490591</v>
+        <v>490598</v>
       </c>
       <c r="R32" t="n">
-        <v>7023786</v>
+        <v>7023986</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4551,7 +4517,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4560,6 +4526,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4580,12 +4547,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4603,45 +4570,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130180069</v>
+        <v>130180042</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>80314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490566</v>
+        <v>490679</v>
       </c>
       <c r="R33" t="n">
-        <v>7023937</v>
+        <v>7023796</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4678,7 +4652,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4687,8 +4661,34 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4705,39 +4705,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130180042</v>
+        <v>130180033</v>
       </c>
       <c r="B34" t="n">
-        <v>80314</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4747,10 +4748,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490679</v>
+        <v>490591</v>
       </c>
       <c r="R34" t="n">
-        <v>7023796</v>
+        <v>7023786</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4787,7 +4788,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4796,7 +4797,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4807,22 +4807,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4942,7 +4942,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130180063</v>
+        <v>130180059</v>
       </c>
       <c r="B36" t="n">
         <v>79180</v>
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490561</v>
+        <v>490614</v>
       </c>
       <c r="R36" t="n">
-        <v>7023986</v>
+        <v>7023878</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5044,7 +5044,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130180059</v>
+        <v>130180063</v>
       </c>
       <c r="B37" t="n">
         <v>79180</v>
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490614</v>
+        <v>490561</v>
       </c>
       <c r="R37" t="n">
-        <v>7023878</v>
+        <v>7023986</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -6029,10 +6029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130180037</v>
+        <v>130180060</v>
       </c>
       <c r="B45" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6040,42 +6040,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490575</v>
+        <v>490647</v>
       </c>
       <c r="R45" t="n">
-        <v>7023818</v>
+        <v>7023943</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6112,7 +6104,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6123,31 +6115,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6266,10 +6233,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130180060</v>
+        <v>130180037</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6277,34 +6244,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490647</v>
+        <v>490575</v>
       </c>
       <c r="R47" t="n">
-        <v>7023943</v>
+        <v>7023818</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6341,7 +6316,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6352,6 +6327,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -7595,7 +7595,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130180076</v>
+        <v>130180066</v>
       </c>
       <c r="B58" t="n">
         <v>79180</v>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490653</v>
+        <v>490497</v>
       </c>
       <c r="R58" t="n">
-        <v>7023898</v>
+        <v>7024012</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gran intill andra hänglavar, i barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7697,7 +7697,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130180066</v>
+        <v>130180076</v>
       </c>
       <c r="B59" t="n">
         <v>79180</v>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490497</v>
+        <v>490653</v>
       </c>
       <c r="R59" t="n">
-        <v>7024012</v>
+        <v>7023898</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran intill andra hänglavar, i barrblandskog.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130180074</v>
+        <v>130180039</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,34 +1284,54 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490581</v>
+        <v>490650</v>
       </c>
       <c r="R7" t="n">
-        <v>7023945</v>
+        <v>7023840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1368,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,6 +1379,36 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1375,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130180039</v>
+        <v>130180074</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,54 +1436,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490650</v>
+        <v>490581</v>
       </c>
       <c r="R8" t="n">
-        <v>7023840</v>
+        <v>7023945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1500,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,36 +1511,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1764,10 +1764,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130180028</v>
+        <v>130180070</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,31 +1775,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490534</v>
+        <v>490547</v>
       </c>
       <c r="R11" t="n">
-        <v>7023897</v>
+        <v>7023925</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1847,7 +1842,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1856,6 +1851,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1876,12 +1872,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1899,7 +1895,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130180070</v>
+        <v>130180064</v>
       </c>
       <c r="B12" t="n">
         <v>79180</v>
@@ -1928,19 +1924,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490547</v>
+        <v>490655</v>
       </c>
       <c r="R12" t="n">
-        <v>7023925</v>
+        <v>7024022</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,7 +1970,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,34 +1979,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2030,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130180064</v>
+        <v>130180028</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,34 +2008,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490655</v>
+        <v>490534</v>
       </c>
       <c r="R13" t="n">
-        <v>7024022</v>
+        <v>7023897</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2105,7 +2080,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2116,6 +2091,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2132,42 +2132,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130180019</v>
+        <v>130180047</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2175,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490488</v>
+        <v>490586</v>
       </c>
       <c r="R14" t="n">
-        <v>7023990</v>
+        <v>7023926</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2215,7 +2211,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,32 +2220,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2267,10 +2244,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130180018</v>
+        <v>130180061</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2278,31 +2255,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2310,10 +2282,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490478</v>
+        <v>490539</v>
       </c>
       <c r="R15" t="n">
-        <v>7024001</v>
+        <v>7024036</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2350,7 +2322,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2359,6 +2331,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2379,12 +2352,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2402,38 +2375,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130180047</v>
+        <v>130180019</v>
       </c>
       <c r="B16" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2441,10 +2418,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490586</v>
+        <v>490488</v>
       </c>
       <c r="R16" t="n">
-        <v>7023926</v>
+        <v>7023990</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2481,7 +2458,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,13 +2467,32 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2514,10 +2510,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130180061</v>
+        <v>130180018</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,26 +2521,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2552,10 +2553,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490539</v>
+        <v>490478</v>
       </c>
       <c r="R17" t="n">
-        <v>7024036</v>
+        <v>7024001</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2592,7 +2593,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,7 +2602,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3059,42 +3059,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130180014</v>
+        <v>130180046</v>
       </c>
       <c r="B21" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3102,10 +3098,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490533</v>
+        <v>490513</v>
       </c>
       <c r="R21" t="n">
-        <v>7024027</v>
+        <v>7023984</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3142,7 +3138,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3151,32 +3147,13 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3194,38 +3171,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180046</v>
+        <v>130180051</v>
       </c>
       <c r="B22" t="n">
-        <v>97791</v>
+        <v>91748</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3233,10 +3209,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490513</v>
+        <v>490648</v>
       </c>
       <c r="R22" t="n">
-        <v>7023984</v>
+        <v>7023846</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3273,7 +3249,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3289,6 +3265,31 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3306,10 +3307,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130180051</v>
+        <v>130180078</v>
       </c>
       <c r="B23" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3317,37 +3318,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490648</v>
+        <v>490660</v>
       </c>
       <c r="R23" t="n">
-        <v>7023846</v>
+        <v>7023791</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3384,7 +3382,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3393,39 +3391,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3442,10 +3409,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130180078</v>
+        <v>130180014</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,34 +3420,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490660</v>
+        <v>490533</v>
       </c>
       <c r="R24" t="n">
-        <v>7023791</v>
+        <v>7024027</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3517,7 +3492,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3528,6 +3503,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3683,7 +3683,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130180031</v>
+        <v>130180036</v>
       </c>
       <c r="B26" t="n">
         <v>57826</v>
@@ -3719,21 +3719,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490546</v>
+        <v>490589</v>
       </c>
       <c r="R26" t="n">
-        <v>7023885</v>
+        <v>7023793</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3770,7 +3766,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3784,7 +3780,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3822,7 +3818,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130180036</v>
+        <v>130180029</v>
       </c>
       <c r="B27" t="n">
         <v>57826</v>
@@ -3858,17 +3854,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490589</v>
+        <v>490543</v>
       </c>
       <c r="R27" t="n">
-        <v>7023793</v>
+        <v>7023888</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, i god mängd på en gran vid en hyggeskant. Troligen  skapade 2025.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -3957,7 +3957,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130180029</v>
+        <v>130180031</v>
       </c>
       <c r="B28" t="n">
         <v>57826</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490543</v>
+        <v>490546</v>
       </c>
       <c r="R28" t="n">
-        <v>7023888</v>
+        <v>7023885</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i god mängd på en gran vid en hyggeskant. Troligen  skapade 2025.</t>
+          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -5044,10 +5044,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130180016</v>
+        <v>130180065</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5055,42 +5055,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490471</v>
+        <v>490576</v>
       </c>
       <c r="R37" t="n">
-        <v>7024008</v>
+        <v>7023998</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5127,7 +5119,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5138,31 +5130,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5179,10 +5146,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130180065</v>
+        <v>130180016</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5190,34 +5157,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490576</v>
+        <v>490471</v>
       </c>
       <c r="R38" t="n">
-        <v>7023998</v>
+        <v>7024008</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5254,7 +5229,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5265,6 +5240,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5281,7 +5281,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130180025</v>
+        <v>130180027</v>
       </c>
       <c r="B39" t="n">
         <v>57826</v>
@@ -5317,17 +5317,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490547</v>
+        <v>490539</v>
       </c>
       <c r="R39" t="n">
-        <v>7023930</v>
+        <v>7023923</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5364,7 +5368,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5416,7 +5420,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130180035</v>
+        <v>130180034</v>
       </c>
       <c r="B40" t="n">
         <v>57826</v>
@@ -5459,10 +5463,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490603</v>
+        <v>490609</v>
       </c>
       <c r="R40" t="n">
-        <v>7023797</v>
+        <v>7023788</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5499,7 +5503,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
+          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5551,7 +5555,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130180027</v>
+        <v>130180025</v>
       </c>
       <c r="B41" t="n">
         <v>57826</v>
@@ -5587,21 +5591,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490539</v>
+        <v>490547</v>
       </c>
       <c r="R41" t="n">
-        <v>7023923</v>
+        <v>7023930</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5690,7 +5690,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130180034</v>
+        <v>130180035</v>
       </c>
       <c r="B42" t="n">
         <v>57826</v>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490609</v>
+        <v>490603</v>
       </c>
       <c r="R42" t="n">
-        <v>7023788</v>
+        <v>7023797</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6029,10 +6029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130180060</v>
+        <v>130180037</v>
       </c>
       <c r="B45" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6040,34 +6040,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490647</v>
+        <v>490575</v>
       </c>
       <c r="R45" t="n">
-        <v>7023943</v>
+        <v>7023818</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6104,7 +6112,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6115,6 +6123,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6131,7 +6164,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130180062</v>
+        <v>130180060</v>
       </c>
       <c r="B46" t="n">
         <v>79180</v>
@@ -6166,10 +6199,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490550</v>
+        <v>490647</v>
       </c>
       <c r="R46" t="n">
-        <v>7023998</v>
+        <v>7023943</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6233,10 +6266,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130180037</v>
+        <v>130180062</v>
       </c>
       <c r="B47" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,42 +6277,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490575</v>
+        <v>490550</v>
       </c>
       <c r="R47" t="n">
-        <v>7023818</v>
+        <v>7023998</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6316,7 +6341,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6327,31 +6352,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6947,38 +6947,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130180044</v>
+        <v>130180024</v>
       </c>
       <c r="B53" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6986,10 +6990,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490663</v>
+        <v>490550</v>
       </c>
       <c r="R53" t="n">
-        <v>7024019</v>
+        <v>7023952</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7026,7 +7030,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid körspår.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7035,13 +7039,32 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7059,7 +7082,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130180024</v>
+        <v>130180030</v>
       </c>
       <c r="B54" t="n">
         <v>57826</v>
@@ -7102,10 +7125,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490550</v>
+        <v>490538</v>
       </c>
       <c r="R54" t="n">
-        <v>7023952</v>
+        <v>7023883</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7142,7 +7165,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid körspår.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7194,42 +7217,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130180030</v>
+        <v>130180044</v>
       </c>
       <c r="B55" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7237,10 +7256,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490538</v>
+        <v>490663</v>
       </c>
       <c r="R55" t="n">
-        <v>7023883</v>
+        <v>7024019</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7277,7 +7296,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7286,32 +7305,13 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130180039</v>
+        <v>130180074</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,54 +1284,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490650</v>
+        <v>490581</v>
       </c>
       <c r="R7" t="n">
-        <v>7023840</v>
+        <v>7023945</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1348,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,36 +1359,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1425,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130180074</v>
+        <v>130180039</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,34 +1386,54 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490581</v>
+        <v>490650</v>
       </c>
       <c r="R8" t="n">
-        <v>7023945</v>
+        <v>7023840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,6 +1481,36 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -2132,38 +2132,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130180047</v>
+        <v>130180019</v>
       </c>
       <c r="B14" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2171,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490586</v>
+        <v>490488</v>
       </c>
       <c r="R14" t="n">
-        <v>7023926</v>
+        <v>7023990</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2211,7 +2215,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,13 +2224,32 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2244,10 +2267,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130180061</v>
+        <v>130180018</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,26 +2278,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2282,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490539</v>
+        <v>490478</v>
       </c>
       <c r="R15" t="n">
-        <v>7024036</v>
+        <v>7024001</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2322,7 +2350,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,7 +2359,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2352,12 +2379,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2375,42 +2402,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130180019</v>
+        <v>130180047</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2418,10 +2441,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490488</v>
+        <v>490586</v>
       </c>
       <c r="R16" t="n">
-        <v>7023990</v>
+        <v>7023926</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2458,7 +2481,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2467,32 +2490,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2510,10 +2514,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130180018</v>
+        <v>130180061</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2521,31 +2525,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2553,10 +2552,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490478</v>
+        <v>490539</v>
       </c>
       <c r="R17" t="n">
-        <v>7024001</v>
+        <v>7024036</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2593,7 +2592,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2602,6 +2601,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3059,38 +3059,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130180046</v>
+        <v>130180014</v>
       </c>
       <c r="B21" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3098,10 +3102,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490513</v>
+        <v>490533</v>
       </c>
       <c r="R21" t="n">
-        <v>7023984</v>
+        <v>7024027</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3138,7 +3142,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3147,13 +3151,32 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3171,37 +3194,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180051</v>
+        <v>130180046</v>
       </c>
       <c r="B22" t="n">
-        <v>91748</v>
+        <v>97791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3209,10 +3233,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490648</v>
+        <v>490513</v>
       </c>
       <c r="R22" t="n">
-        <v>7023846</v>
+        <v>7023984</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3249,7 +3273,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3265,31 +3289,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3307,10 +3306,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130180078</v>
+        <v>130180051</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>91748</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3318,34 +3317,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490660</v>
+        <v>490648</v>
       </c>
       <c r="R23" t="n">
-        <v>7023791</v>
+        <v>7023846</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3382,7 +3384,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3391,8 +3393,39 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3409,10 +3442,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130180014</v>
+        <v>130180078</v>
       </c>
       <c r="B24" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,42 +3453,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490533</v>
+        <v>490660</v>
       </c>
       <c r="R24" t="n">
-        <v>7024027</v>
+        <v>7023791</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3492,7 +3517,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3503,31 +3528,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3683,7 +3683,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130180036</v>
+        <v>130180031</v>
       </c>
       <c r="B26" t="n">
         <v>57826</v>
@@ -3719,17 +3719,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490589</v>
+        <v>490546</v>
       </c>
       <c r="R26" t="n">
-        <v>7023793</v>
+        <v>7023885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3766,7 +3770,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3780,7 +3784,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3818,7 +3822,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130180029</v>
+        <v>130180036</v>
       </c>
       <c r="B27" t="n">
         <v>57826</v>
@@ -3854,21 +3858,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490543</v>
+        <v>490589</v>
       </c>
       <c r="R27" t="n">
-        <v>7023888</v>
+        <v>7023793</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i god mängd på en gran vid en hyggeskant. Troligen  skapade 2025.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -3957,7 +3957,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130180031</v>
+        <v>130180029</v>
       </c>
       <c r="B28" t="n">
         <v>57826</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490546</v>
+        <v>490543</v>
       </c>
       <c r="R28" t="n">
-        <v>7023885</v>
+        <v>7023888</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, i god mängd på en gran vid en hyggeskant. Troligen  skapade 2025.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4096,10 +4096,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130180033</v>
+        <v>130180009</v>
       </c>
       <c r="B29" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,29 +4107,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4139,10 +4138,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490591</v>
+        <v>490651</v>
       </c>
       <c r="R29" t="n">
-        <v>7023786</v>
+        <v>7024020</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4179,7 +4178,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I en granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4188,6 +4187,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4208,12 +4208,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4231,7 +4231,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130180009</v>
+        <v>130180008</v>
       </c>
       <c r="B30" t="n">
         <v>91728</v>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490651</v>
+        <v>490598</v>
       </c>
       <c r="R30" t="n">
-        <v>7024020</v>
+        <v>7023986</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>I en granlåga i barrblandskog.</t>
+          <t>I granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4366,10 +4366,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130180008</v>
+        <v>130180069</v>
       </c>
       <c r="B31" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4377,41 +4377,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490598</v>
+        <v>490566</v>
       </c>
       <c r="R31" t="n">
-        <v>7023986</v>
+        <v>7023937</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4448,7 +4441,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>I granlåga i barrblandskog.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4457,34 +4450,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4501,7 +4468,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180069</v>
+        <v>130180072</v>
       </c>
       <c r="B32" t="n">
         <v>79180</v>
@@ -4536,10 +4503,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490566</v>
+        <v>490590</v>
       </c>
       <c r="R32" t="n">
-        <v>7023937</v>
+        <v>7023801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4576,7 +4543,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4603,45 +4570,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130180072</v>
+        <v>130180042</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>80314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490590</v>
+        <v>490679</v>
       </c>
       <c r="R33" t="n">
-        <v>7023801</v>
+        <v>7023796</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4678,7 +4652,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4687,8 +4661,34 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4705,39 +4705,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130180042</v>
+        <v>130180033</v>
       </c>
       <c r="B34" t="n">
-        <v>80314</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4747,10 +4748,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490679</v>
+        <v>490591</v>
       </c>
       <c r="R34" t="n">
-        <v>7023796</v>
+        <v>7023786</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4787,7 +4788,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4796,7 +4797,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4807,22 +4807,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130180065</v>
+        <v>130180016</v>
       </c>
       <c r="B37" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5055,34 +5055,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490576</v>
+        <v>490471</v>
       </c>
       <c r="R37" t="n">
-        <v>7023998</v>
+        <v>7024008</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5119,7 +5127,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5130,6 +5138,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5146,10 +5179,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130180016</v>
+        <v>130180065</v>
       </c>
       <c r="B38" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5157,42 +5190,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490471</v>
+        <v>490576</v>
       </c>
       <c r="R38" t="n">
-        <v>7024008</v>
+        <v>7023998</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5229,7 +5254,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5240,31 +5265,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5281,7 +5281,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130180027</v>
+        <v>130180025</v>
       </c>
       <c r="B39" t="n">
         <v>57826</v>
@@ -5317,21 +5317,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490539</v>
+        <v>490547</v>
       </c>
       <c r="R39" t="n">
-        <v>7023923</v>
+        <v>7023930</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5368,7 +5364,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5420,7 +5416,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130180034</v>
+        <v>130180035</v>
       </c>
       <c r="B40" t="n">
         <v>57826</v>
@@ -5463,10 +5459,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490609</v>
+        <v>490603</v>
       </c>
       <c r="R40" t="n">
-        <v>7023788</v>
+        <v>7023797</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5503,7 +5499,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5555,7 +5551,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130180025</v>
+        <v>130180027</v>
       </c>
       <c r="B41" t="n">
         <v>57826</v>
@@ -5591,17 +5587,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490547</v>
+        <v>490539</v>
       </c>
       <c r="R41" t="n">
-        <v>7023930</v>
+        <v>7023923</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5690,7 +5690,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130180035</v>
+        <v>130180034</v>
       </c>
       <c r="B42" t="n">
         <v>57826</v>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490603</v>
+        <v>490609</v>
       </c>
       <c r="R42" t="n">
-        <v>7023797</v>
+        <v>7023788</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
+          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6029,10 +6029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130180037</v>
+        <v>130180060</v>
       </c>
       <c r="B45" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6040,42 +6040,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490575</v>
+        <v>490647</v>
       </c>
       <c r="R45" t="n">
-        <v>7023818</v>
+        <v>7023943</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6112,7 +6104,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6123,31 +6115,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6164,7 +6131,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130180060</v>
+        <v>130180062</v>
       </c>
       <c r="B46" t="n">
         <v>79180</v>
@@ -6199,10 +6166,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490647</v>
+        <v>490550</v>
       </c>
       <c r="R46" t="n">
-        <v>7023943</v>
+        <v>7023998</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6266,10 +6233,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130180062</v>
+        <v>130180037</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6277,34 +6244,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490550</v>
+        <v>490575</v>
       </c>
       <c r="R47" t="n">
-        <v>7023998</v>
+        <v>7023818</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6341,7 +6316,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6352,6 +6327,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130180074</v>
+        <v>130180039</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,34 +1284,54 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490581</v>
+        <v>490650</v>
       </c>
       <c r="R7" t="n">
-        <v>7023945</v>
+        <v>7023840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1368,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,6 +1379,36 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1375,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130180039</v>
+        <v>130180074</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,54 +1436,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490650</v>
+        <v>490581</v>
       </c>
       <c r="R8" t="n">
-        <v>7023840</v>
+        <v>7023945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1500,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,36 +1511,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1764,10 +1764,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130180070</v>
+        <v>130180028</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,26 +1775,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490547</v>
+        <v>490534</v>
       </c>
       <c r="R11" t="n">
-        <v>7023925</v>
+        <v>7023897</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,7 +1847,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,7 +1856,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1872,12 +1876,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1895,7 +1899,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130180064</v>
+        <v>130180070</v>
       </c>
       <c r="B12" t="n">
         <v>79180</v>
@@ -1924,16 +1928,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490655</v>
+        <v>490547</v>
       </c>
       <c r="R12" t="n">
-        <v>7024022</v>
+        <v>7023925</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1970,7 +1977,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,8 +1986,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1997,10 +2030,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130180028</v>
+        <v>130180064</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,42 +2041,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490534</v>
+        <v>490655</v>
       </c>
       <c r="R13" t="n">
-        <v>7023897</v>
+        <v>7024022</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2080,7 +2105,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,31 +2116,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2132,42 +2132,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130180019</v>
+        <v>130180047</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2175,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490488</v>
+        <v>490586</v>
       </c>
       <c r="R14" t="n">
-        <v>7023990</v>
+        <v>7023926</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2215,7 +2211,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,32 +2220,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2267,10 +2244,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130180018</v>
+        <v>130180061</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2278,31 +2255,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2310,10 +2282,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490478</v>
+        <v>490539</v>
       </c>
       <c r="R15" t="n">
-        <v>7024001</v>
+        <v>7024036</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2350,7 +2322,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2359,6 +2331,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2379,12 +2352,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2402,38 +2375,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130180047</v>
+        <v>130180019</v>
       </c>
       <c r="B16" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2441,10 +2418,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490586</v>
+        <v>490488</v>
       </c>
       <c r="R16" t="n">
-        <v>7023926</v>
+        <v>7023990</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2481,7 +2458,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,13 +2467,32 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2514,10 +2510,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130180061</v>
+        <v>130180018</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,26 +2521,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2552,10 +2553,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490539</v>
+        <v>490478</v>
       </c>
       <c r="R17" t="n">
-        <v>7024036</v>
+        <v>7024001</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2592,7 +2593,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,7 +2602,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3059,42 +3059,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130180014</v>
+        <v>130180046</v>
       </c>
       <c r="B21" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3102,10 +3098,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490533</v>
+        <v>490513</v>
       </c>
       <c r="R21" t="n">
-        <v>7024027</v>
+        <v>7023984</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3142,7 +3138,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3151,32 +3147,13 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3194,38 +3171,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180046</v>
+        <v>130180051</v>
       </c>
       <c r="B22" t="n">
-        <v>97791</v>
+        <v>91748</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3233,10 +3209,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490513</v>
+        <v>490648</v>
       </c>
       <c r="R22" t="n">
-        <v>7023984</v>
+        <v>7023846</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3273,7 +3249,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3289,6 +3265,31 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3306,10 +3307,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130180051</v>
+        <v>130180078</v>
       </c>
       <c r="B23" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3317,37 +3318,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490648</v>
+        <v>490660</v>
       </c>
       <c r="R23" t="n">
-        <v>7023846</v>
+        <v>7023791</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3384,7 +3382,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3393,39 +3391,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3442,10 +3409,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130180078</v>
+        <v>130180014</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,34 +3420,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490660</v>
+        <v>490533</v>
       </c>
       <c r="R24" t="n">
-        <v>7023791</v>
+        <v>7024027</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3517,7 +3492,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3528,6 +3503,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -5044,10 +5044,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130180016</v>
+        <v>130180065</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5055,42 +5055,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490471</v>
+        <v>490576</v>
       </c>
       <c r="R37" t="n">
-        <v>7024008</v>
+        <v>7023998</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5127,7 +5119,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5138,31 +5130,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5179,10 +5146,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130180065</v>
+        <v>130180016</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5190,34 +5157,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490576</v>
+        <v>490471</v>
       </c>
       <c r="R38" t="n">
-        <v>7023998</v>
+        <v>7024008</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5254,7 +5229,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5265,6 +5240,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5281,7 +5281,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130180025</v>
+        <v>130180027</v>
       </c>
       <c r="B39" t="n">
         <v>57826</v>
@@ -5317,17 +5317,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490547</v>
+        <v>490539</v>
       </c>
       <c r="R39" t="n">
-        <v>7023930</v>
+        <v>7023923</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5364,7 +5368,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5416,7 +5420,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130180035</v>
+        <v>130180034</v>
       </c>
       <c r="B40" t="n">
         <v>57826</v>
@@ -5459,10 +5463,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490603</v>
+        <v>490609</v>
       </c>
       <c r="R40" t="n">
-        <v>7023797</v>
+        <v>7023788</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5499,7 +5503,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
+          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5551,7 +5555,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130180027</v>
+        <v>130180025</v>
       </c>
       <c r="B41" t="n">
         <v>57826</v>
@@ -5587,21 +5591,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490539</v>
+        <v>490547</v>
       </c>
       <c r="R41" t="n">
-        <v>7023923</v>
+        <v>7023930</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5690,7 +5690,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130180034</v>
+        <v>130180035</v>
       </c>
       <c r="B42" t="n">
         <v>57826</v>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490609</v>
+        <v>490603</v>
       </c>
       <c r="R42" t="n">
-        <v>7023788</v>
+        <v>7023797</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6029,10 +6029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130180060</v>
+        <v>130180037</v>
       </c>
       <c r="B45" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6040,34 +6040,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490647</v>
+        <v>490575</v>
       </c>
       <c r="R45" t="n">
-        <v>7023943</v>
+        <v>7023818</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6104,7 +6112,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6115,6 +6123,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6131,7 +6164,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130180062</v>
+        <v>130180060</v>
       </c>
       <c r="B46" t="n">
         <v>79180</v>
@@ -6166,10 +6199,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490550</v>
+        <v>490647</v>
       </c>
       <c r="R46" t="n">
-        <v>7023998</v>
+        <v>7023943</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6233,10 +6266,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130180037</v>
+        <v>130180062</v>
       </c>
       <c r="B47" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,42 +6277,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490575</v>
+        <v>490550</v>
       </c>
       <c r="R47" t="n">
-        <v>7023818</v>
+        <v>7023998</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6316,7 +6341,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6327,31 +6352,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6947,42 +6947,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130180024</v>
+        <v>130180044</v>
       </c>
       <c r="B53" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6990,10 +6986,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490550</v>
+        <v>490663</v>
       </c>
       <c r="R53" t="n">
-        <v>7023952</v>
+        <v>7024019</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7030,7 +7026,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid körspår.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7039,32 +7035,13 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7082,7 +7059,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130180030</v>
+        <v>130180024</v>
       </c>
       <c r="B54" t="n">
         <v>57826</v>
@@ -7125,10 +7102,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490538</v>
+        <v>490550</v>
       </c>
       <c r="R54" t="n">
-        <v>7023883</v>
+        <v>7023952</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7165,7 +7142,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid körspår.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7217,38 +7194,42 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130180044</v>
+        <v>130180030</v>
       </c>
       <c r="B55" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7256,10 +7237,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490663</v>
+        <v>490538</v>
       </c>
       <c r="R55" t="n">
-        <v>7024019</v>
+        <v>7023883</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7296,7 +7277,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7305,13 +7286,32 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>130180073</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130180039</v>
+        <v>130180074</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,54 +1284,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490650</v>
+        <v>490581</v>
       </c>
       <c r="R7" t="n">
-        <v>7023840</v>
+        <v>7023945</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1348,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,36 +1359,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1425,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130180074</v>
+        <v>130180039</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,34 +1386,54 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490581</v>
+        <v>490650</v>
       </c>
       <c r="R8" t="n">
-        <v>7023945</v>
+        <v>7023840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,6 +1481,36 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1530,7 +1530,7 @@
         <v>130180071</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130180028</v>
+        <v>130180070</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,31 +1775,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490534</v>
+        <v>490547</v>
       </c>
       <c r="R11" t="n">
-        <v>7023897</v>
+        <v>7023925</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1847,7 +1842,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1856,6 +1851,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1876,12 +1872,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1899,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130180070</v>
+        <v>130180064</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,19 +1924,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490547</v>
+        <v>490655</v>
       </c>
       <c r="R12" t="n">
-        <v>7023925</v>
+        <v>7024022</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,7 +1970,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,34 +1979,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2030,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130180064</v>
+        <v>130180028</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,34 +2008,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490655</v>
+        <v>490534</v>
       </c>
       <c r="R13" t="n">
-        <v>7024022</v>
+        <v>7023897</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2105,7 +2080,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2116,6 +2091,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2132,38 +2132,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130180047</v>
+        <v>130180061</v>
       </c>
       <c r="B14" t="n">
-        <v>97791</v>
+        <v>79183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2171,10 +2170,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490586</v>
+        <v>490539</v>
       </c>
       <c r="R14" t="n">
-        <v>7023926</v>
+        <v>7024036</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2211,7 +2210,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2227,6 +2226,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2244,10 +2263,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130180061</v>
+        <v>130180019</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,26 +2274,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2282,10 +2306,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490539</v>
+        <v>490488</v>
       </c>
       <c r="R15" t="n">
-        <v>7024036</v>
+        <v>7023990</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2322,7 +2346,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,7 +2355,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2352,12 +2375,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2375,7 +2398,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130180019</v>
+        <v>130180018</v>
       </c>
       <c r="B16" t="n">
         <v>57826</v>
@@ -2418,10 +2441,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490488</v>
+        <v>490478</v>
       </c>
       <c r="R16" t="n">
-        <v>7023990</v>
+        <v>7024001</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2510,42 +2533,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130180018</v>
+        <v>130180047</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>97794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2553,10 +2572,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490478</v>
+        <v>490586</v>
       </c>
       <c r="R17" t="n">
-        <v>7024001</v>
+        <v>7023926</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2593,7 +2612,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2602,32 +2621,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130180022</v>
+        <v>130180038</v>
       </c>
       <c r="B18" t="n">
         <v>57826</v>
@@ -2678,20 +2678,24 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490522</v>
+        <v>490648</v>
       </c>
       <c r="R18" t="n">
-        <v>7023957</v>
+        <v>7023846</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2728,14 +2732,14 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
+          <t>Gamla bohål i en stående död gran med full längd som har fruktkroppar av granticka. Ett bohål (diameter 4 cm) på 1,8 meters höjd, och ett bohål (diameter 4,5 cm) på 2,1 meters höjd. Finns även fler bohål och andra hackade hål högre upp i granstammen. Troligen bohål som tidigare använts av tretåig hackspett. Hålens storlek och att en hona av tretåig hackspett födosökte precis intill styrker detta.</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
@@ -2745,6 +2749,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2757,12 +2766,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2915,7 +2924,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130180038</v>
+        <v>130180022</v>
       </c>
       <c r="B20" t="n">
         <v>57826</v>
@@ -2948,24 +2957,20 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490648</v>
+        <v>490522</v>
       </c>
       <c r="R20" t="n">
-        <v>7023846</v>
+        <v>7023957</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3002,14 +3007,14 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gamla bohål i en stående död gran med full längd som har fruktkroppar av granticka. Ett bohål (diameter 4 cm) på 1,8 meters höjd, och ett bohål (diameter 4,5 cm) på 2,1 meters höjd. Finns även fler bohål och andra hackade hål högre upp i granstammen. Troligen bohål som tidigare använts av tretåig hackspett. Hålens storlek och att en hona av tretåig hackspett födosökte precis intill styrker detta.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -3019,11 +3024,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3036,12 +3036,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3059,49 +3059,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130180046</v>
+        <v>130180020</v>
       </c>
       <c r="B21" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490513</v>
+        <v>490494</v>
       </c>
       <c r="R21" t="n">
-        <v>7023984</v>
+        <v>7023983</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3138,7 +3146,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3147,13 +3155,32 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3171,10 +3198,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180051</v>
+        <v>130180014</v>
       </c>
       <c r="B22" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3182,24 +3209,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3209,10 +3241,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490648</v>
+        <v>490533</v>
       </c>
       <c r="R22" t="n">
-        <v>7023846</v>
+        <v>7024027</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3249,7 +3281,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3258,7 +3290,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3267,11 +3298,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3284,12 +3310,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3307,10 +3333,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130180078</v>
+        <v>130180051</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>91751</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3318,34 +3344,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490660</v>
+        <v>490648</v>
       </c>
       <c r="R23" t="n">
-        <v>7023791</v>
+        <v>7023846</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3382,7 +3411,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3391,8 +3420,39 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3409,10 +3469,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130180014</v>
+        <v>130180078</v>
       </c>
       <c r="B24" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,42 +3480,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490533</v>
+        <v>490660</v>
       </c>
       <c r="R24" t="n">
-        <v>7024027</v>
+        <v>7023791</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3492,7 +3544,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3503,31 +3555,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3544,57 +3571,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130180020</v>
+        <v>130180046</v>
       </c>
       <c r="B25" t="n">
-        <v>57826</v>
+        <v>97794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490494</v>
+        <v>490513</v>
       </c>
       <c r="R25" t="n">
-        <v>7023983</v>
+        <v>7023984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3631,7 +3650,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3640,32 +3659,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130180031</v>
+        <v>130180036</v>
       </c>
       <c r="B26" t="n">
         <v>57826</v>
@@ -3719,21 +3719,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490546</v>
+        <v>490589</v>
       </c>
       <c r="R26" t="n">
-        <v>7023885</v>
+        <v>7023793</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3770,7 +3766,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3784,7 +3780,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3822,7 +3818,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130180036</v>
+        <v>130180031</v>
       </c>
       <c r="B27" t="n">
         <v>57826</v>
@@ -3858,17 +3854,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490589</v>
+        <v>490546</v>
       </c>
       <c r="R27" t="n">
-        <v>7023793</v>
+        <v>7023885</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4096,39 +4096,39 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130180009</v>
+        <v>130180042</v>
       </c>
       <c r="B29" t="n">
-        <v>91728</v>
+        <v>80317</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490651</v>
+        <v>490679</v>
       </c>
       <c r="R29" t="n">
-        <v>7024020</v>
+        <v>7023796</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I en granlåga i barrblandskog.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4198,22 +4198,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130180008</v>
+        <v>130180009</v>
       </c>
       <c r="B30" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490598</v>
+        <v>490651</v>
       </c>
       <c r="R30" t="n">
-        <v>7023986</v>
+        <v>7024020</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>I granlåga i barrblandskog.</t>
+          <t>I en granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4366,10 +4366,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130180069</v>
+        <v>130180008</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>91731</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4377,34 +4377,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490566</v>
+        <v>490598</v>
       </c>
       <c r="R31" t="n">
-        <v>7023937</v>
+        <v>7023986</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4441,7 +4448,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>I granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4450,8 +4457,34 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4468,10 +4501,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180072</v>
+        <v>130180069</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4503,10 +4536,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490590</v>
+        <v>490566</v>
       </c>
       <c r="R32" t="n">
-        <v>7023801</v>
+        <v>7023937</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4543,7 +4576,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4570,52 +4603,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130180042</v>
+        <v>130180072</v>
       </c>
       <c r="B33" t="n">
-        <v>80314</v>
+        <v>79183</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490679</v>
+        <v>490590</v>
       </c>
       <c r="R33" t="n">
-        <v>7023796</v>
+        <v>7023801</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4652,7 +4678,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4661,34 +4687,8 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4840,10 +4840,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130180059</v>
+        <v>130180065</v>
       </c>
       <c r="B35" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490614</v>
+        <v>490576</v>
       </c>
       <c r="R35" t="n">
-        <v>7023878</v>
+        <v>7023998</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4942,10 +4942,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130180063</v>
+        <v>130180059</v>
       </c>
       <c r="B36" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490561</v>
+        <v>490614</v>
       </c>
       <c r="R36" t="n">
-        <v>7023986</v>
+        <v>7023878</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5044,10 +5044,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130180065</v>
+        <v>130180063</v>
       </c>
       <c r="B37" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490576</v>
+        <v>490561</v>
       </c>
       <c r="R37" t="n">
-        <v>7023998</v>
+        <v>7023986</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5281,7 +5281,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130180027</v>
+        <v>130180025</v>
       </c>
       <c r="B39" t="n">
         <v>57826</v>
@@ -5317,21 +5317,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490539</v>
+        <v>490547</v>
       </c>
       <c r="R39" t="n">
-        <v>7023923</v>
+        <v>7023930</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5368,7 +5364,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5420,7 +5416,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130180034</v>
+        <v>130180035</v>
       </c>
       <c r="B40" t="n">
         <v>57826</v>
@@ -5463,10 +5459,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490609</v>
+        <v>490603</v>
       </c>
       <c r="R40" t="n">
-        <v>7023788</v>
+        <v>7023797</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5503,7 +5499,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5555,7 +5551,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130180025</v>
+        <v>130180034</v>
       </c>
       <c r="B41" t="n">
         <v>57826</v>
@@ -5598,10 +5594,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490547</v>
+        <v>490609</v>
       </c>
       <c r="R41" t="n">
-        <v>7023930</v>
+        <v>7023788</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5638,7 +5634,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5690,7 +5686,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130180035</v>
+        <v>130180027</v>
       </c>
       <c r="B42" t="n">
         <v>57826</v>
@@ -5726,17 +5722,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490603</v>
+        <v>490539</v>
       </c>
       <c r="R42" t="n">
-        <v>7023797</v>
+        <v>7023923</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
+          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5828,7 +5828,7 @@
         <v>130180068</v>
       </c>
       <c r="B43" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>130180077</v>
       </c>
       <c r="B44" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6029,10 +6029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130180037</v>
+        <v>130180060</v>
       </c>
       <c r="B45" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6040,42 +6040,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490575</v>
+        <v>490647</v>
       </c>
       <c r="R45" t="n">
-        <v>7023818</v>
+        <v>7023943</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6112,7 +6104,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6123,31 +6115,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6164,10 +6131,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130180060</v>
+        <v>130180062</v>
       </c>
       <c r="B46" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6199,10 +6166,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490647</v>
+        <v>490550</v>
       </c>
       <c r="R46" t="n">
-        <v>7023943</v>
+        <v>7023998</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6266,10 +6233,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130180062</v>
+        <v>130180037</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6277,34 +6244,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490550</v>
+        <v>490575</v>
       </c>
       <c r="R47" t="n">
-        <v>7023998</v>
+        <v>7023818</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6341,7 +6316,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6352,6 +6327,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6371,7 +6371,7 @@
         <v>130180045</v>
       </c>
       <c r="B48" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>130180075</v>
       </c>
       <c r="B49" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>130180067</v>
       </c>
       <c r="B50" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6947,38 +6947,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130180044</v>
+        <v>130180030</v>
       </c>
       <c r="B53" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6986,10 +6990,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490663</v>
+        <v>490538</v>
       </c>
       <c r="R53" t="n">
-        <v>7024019</v>
+        <v>7023883</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7026,7 +7030,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7035,13 +7039,32 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7194,42 +7217,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130180030</v>
+        <v>130180044</v>
       </c>
       <c r="B55" t="n">
-        <v>57826</v>
+        <v>97794</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7237,10 +7256,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490538</v>
+        <v>490663</v>
       </c>
       <c r="R55" t="n">
-        <v>7023883</v>
+        <v>7024019</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7277,7 +7296,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7286,32 +7305,13 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130180015</v>
+        <v>130180052</v>
       </c>
       <c r="B56" t="n">
-        <v>57826</v>
+        <v>91751</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7340,29 +7340,24 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7372,10 +7367,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490474</v>
+        <v>490615</v>
       </c>
       <c r="R56" t="n">
-        <v>7024009</v>
+        <v>7023767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7412,7 +7407,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I stubbe och låga av knäckt gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7421,6 +7416,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7441,12 +7437,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7464,10 +7460,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130180052</v>
+        <v>130180015</v>
       </c>
       <c r="B57" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7475,24 +7471,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7502,10 +7503,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490615</v>
+        <v>490474</v>
       </c>
       <c r="R57" t="n">
-        <v>7023767</v>
+        <v>7024009</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7542,7 +7543,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>I stubbe och låga av knäckt gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7551,7 +7552,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130180066</v>
+        <v>130180032</v>
       </c>
       <c r="B58" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7606,34 +7606,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490497</v>
+        <v>490566</v>
       </c>
       <c r="R58" t="n">
-        <v>7024012</v>
+        <v>7023832</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7670,7 +7682,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en smal gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7681,6 +7693,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7697,10 +7734,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130180032</v>
+        <v>130180076</v>
       </c>
       <c r="B59" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7708,46 +7745,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490566</v>
+        <v>490653</v>
       </c>
       <c r="R59" t="n">
-        <v>7023832</v>
+        <v>7023898</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7784,7 +7809,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en smal gran vid en hyggeskant.</t>
+          <t>På gran intill andra hänglavar, i barrblandskog.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7795,31 +7820,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7836,10 +7836,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130180076</v>
+        <v>130180066</v>
       </c>
       <c r="B60" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7871,10 +7871,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490653</v>
+        <v>490497</v>
       </c>
       <c r="R60" t="n">
-        <v>7023898</v>
+        <v>7024012</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gran intill andra hänglavar, i barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
         <v>130180040</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>130180073</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130180041</v>
+        <v>130180017</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>57852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,50 +1021,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490626</v>
+        <v>490478</v>
       </c>
       <c r="R5" t="n">
-        <v>7023887</v>
+        <v>7024005</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 1 individ, ev. fler. Fyndplatsen finns i flerskiktad äldre barrblandskog.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,9 +1110,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre barrblandskog.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1138,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130180017</v>
+        <v>130180041</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>58011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,42 +1156,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490478</v>
+        <v>490626</v>
       </c>
       <c r="R6" t="n">
-        <v>7024005</v>
+        <v>7023887</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1236,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 1 individ, ev. fler. Fyndplatsen finns i flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,24 +1253,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1276,7 +1276,7 @@
         <v>130180074</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>130180039</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>130180071</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>130180021</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130180070</v>
+        <v>130180028</v>
       </c>
       <c r="B11" t="n">
-        <v>79183</v>
+        <v>57852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,26 +1775,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490547</v>
+        <v>490534</v>
       </c>
       <c r="R11" t="n">
-        <v>7023925</v>
+        <v>7023897</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,7 +1847,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,7 +1856,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1872,12 +1876,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1895,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130180064</v>
+        <v>130180070</v>
       </c>
       <c r="B12" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,16 +1928,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490655</v>
+        <v>490547</v>
       </c>
       <c r="R12" t="n">
-        <v>7024022</v>
+        <v>7023925</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1970,7 +1977,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,8 +1986,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1997,10 +2030,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130180028</v>
+        <v>130180064</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>79209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,42 +2041,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490534</v>
+        <v>490655</v>
       </c>
       <c r="R13" t="n">
-        <v>7023897</v>
+        <v>7024022</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2080,7 +2105,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,31 +2116,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2135,7 +2135,7 @@
         <v>130180061</v>
       </c>
       <c r="B14" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>130180019</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>130180018</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>130180047</v>
       </c>
       <c r="B17" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>130180038</v>
       </c>
       <c r="B18" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>130180023</v>
       </c>
       <c r="B19" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>130180022</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>130180020</v>
       </c>
       <c r="B21" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>130180014</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3333,37 +3333,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130180051</v>
+        <v>130180046</v>
       </c>
       <c r="B23" t="n">
-        <v>91751</v>
+        <v>97820</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3371,10 +3372,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490648</v>
+        <v>490513</v>
       </c>
       <c r="R23" t="n">
-        <v>7023846</v>
+        <v>7023984</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3411,7 +3412,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3427,31 +3428,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3469,10 +3445,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130180078</v>
+        <v>130180051</v>
       </c>
       <c r="B24" t="n">
-        <v>79183</v>
+        <v>91777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3480,34 +3456,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490660</v>
+        <v>490648</v>
       </c>
       <c r="R24" t="n">
-        <v>7023791</v>
+        <v>7023846</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3544,7 +3523,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3553,8 +3532,39 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3571,49 +3581,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130180046</v>
+        <v>130180078</v>
       </c>
       <c r="B25" t="n">
-        <v>97794</v>
+        <v>79209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490513</v>
+        <v>490660</v>
       </c>
       <c r="R25" t="n">
-        <v>7023984</v>
+        <v>7023791</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3650,7 +3656,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3659,14 +3665,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3686,7 +3686,7 @@
         <v>130180036</v>
       </c>
       <c r="B26" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>130180031</v>
       </c>
       <c r="B27" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>130180029</v>
       </c>
       <c r="B28" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4096,39 +4096,40 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130180042</v>
+        <v>130180033</v>
       </c>
       <c r="B29" t="n">
-        <v>80317</v>
+        <v>57852</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4138,10 +4139,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490679</v>
+        <v>490591</v>
       </c>
       <c r="R29" t="n">
-        <v>7023796</v>
+        <v>7023786</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4178,7 +4179,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4187,7 +4188,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4198,22 +4198,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130180009</v>
+        <v>130180072</v>
       </c>
       <c r="B30" t="n">
-        <v>91731</v>
+        <v>79209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4242,41 +4242,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490651</v>
+        <v>490590</v>
       </c>
       <c r="R30" t="n">
-        <v>7024020</v>
+        <v>7023801</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4313,7 +4306,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>I en granlåga i barrblandskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4322,34 +4315,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4366,10 +4333,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130180008</v>
+        <v>130180069</v>
       </c>
       <c r="B31" t="n">
-        <v>91731</v>
+        <v>79209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4377,41 +4344,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490598</v>
+        <v>490566</v>
       </c>
       <c r="R31" t="n">
-        <v>7023986</v>
+        <v>7023937</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4448,7 +4408,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>I granlåga i barrblandskog.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4457,34 +4417,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4501,45 +4435,52 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180069</v>
+        <v>130180042</v>
       </c>
       <c r="B32" t="n">
-        <v>79183</v>
+        <v>80343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490566</v>
+        <v>490679</v>
       </c>
       <c r="R32" t="n">
-        <v>7023937</v>
+        <v>7023796</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4576,7 +4517,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4585,8 +4526,34 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4603,10 +4570,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130180072</v>
+        <v>130180009</v>
       </c>
       <c r="B33" t="n">
-        <v>79183</v>
+        <v>91757</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4614,34 +4581,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490590</v>
+        <v>490651</v>
       </c>
       <c r="R33" t="n">
-        <v>7023801</v>
+        <v>7024020</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4678,7 +4652,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>I en granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4687,8 +4661,34 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4705,10 +4705,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130180033</v>
+        <v>130180008</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>91757</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4716,29 +4716,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4748,10 +4747,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490591</v>
+        <v>490598</v>
       </c>
       <c r="R34" t="n">
-        <v>7023786</v>
+        <v>7023986</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4788,7 +4787,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4797,6 +4796,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130180065</v>
+        <v>130180059</v>
       </c>
       <c r="B35" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490576</v>
+        <v>490614</v>
       </c>
       <c r="R35" t="n">
-        <v>7023998</v>
+        <v>7023878</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4942,10 +4942,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130180059</v>
+        <v>130180063</v>
       </c>
       <c r="B36" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490614</v>
+        <v>490561</v>
       </c>
       <c r="R36" t="n">
-        <v>7023878</v>
+        <v>7023986</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5044,10 +5044,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130180063</v>
+        <v>130180065</v>
       </c>
       <c r="B37" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490561</v>
+        <v>490576</v>
       </c>
       <c r="R37" t="n">
-        <v>7023986</v>
+        <v>7023998</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5149,7 +5149,7 @@
         <v>130180016</v>
       </c>
       <c r="B38" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>130180025</v>
       </c>
       <c r="B39" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>130180035</v>
       </c>
       <c r="B40" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>130180034</v>
       </c>
       <c r="B41" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>130180027</v>
       </c>
       <c r="B42" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5825,10 +5825,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130180068</v>
+        <v>130180077</v>
       </c>
       <c r="B43" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490541</v>
+        <v>490626</v>
       </c>
       <c r="R43" t="n">
-        <v>7023968</v>
+        <v>7023902</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>Enstaka på gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5927,10 +5927,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130180077</v>
+        <v>130180068</v>
       </c>
       <c r="B44" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490626</v>
+        <v>490541</v>
       </c>
       <c r="R44" t="n">
-        <v>7023902</v>
+        <v>7023968</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Enstaka på gran i äldre barrblandskog.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6029,10 +6029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130180060</v>
+        <v>130180062</v>
       </c>
       <c r="B45" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490647</v>
+        <v>490550</v>
       </c>
       <c r="R45" t="n">
-        <v>7023943</v>
+        <v>7023998</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6131,10 +6131,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130180062</v>
+        <v>130180037</v>
       </c>
       <c r="B46" t="n">
-        <v>79183</v>
+        <v>57852</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6142,34 +6142,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490550</v>
+        <v>490575</v>
       </c>
       <c r="R46" t="n">
-        <v>7023998</v>
+        <v>7023818</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6206,7 +6214,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6217,6 +6225,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6233,10 +6266,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130180037</v>
+        <v>130180060</v>
       </c>
       <c r="B47" t="n">
-        <v>57826</v>
+        <v>79209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,42 +6277,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490575</v>
+        <v>490647</v>
       </c>
       <c r="R47" t="n">
-        <v>7023818</v>
+        <v>7023943</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6316,7 +6341,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6327,31 +6352,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6371,7 +6371,7 @@
         <v>130180045</v>
       </c>
       <c r="B48" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>130180075</v>
       </c>
       <c r="B49" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>130180067</v>
       </c>
       <c r="B50" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>130180043</v>
       </c>
       <c r="B51" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>130180026</v>
       </c>
       <c r="B52" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>130180030</v>
       </c>
       <c r="B53" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>130180024</v>
       </c>
       <c r="B54" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>130180044</v>
       </c>
       <c r="B55" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7329,10 +7329,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130180052</v>
+        <v>130180015</v>
       </c>
       <c r="B56" t="n">
-        <v>91751</v>
+        <v>57852</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7340,24 +7340,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7367,10 +7372,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490615</v>
+        <v>490474</v>
       </c>
       <c r="R56" t="n">
-        <v>7023767</v>
+        <v>7024009</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7407,7 +7412,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>I stubbe och låga av knäckt gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7416,7 +7421,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7437,12 +7441,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7460,10 +7464,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130180015</v>
+        <v>130180052</v>
       </c>
       <c r="B57" t="n">
-        <v>57826</v>
+        <v>91777</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7471,29 +7475,24 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7503,10 +7502,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490474</v>
+        <v>490615</v>
       </c>
       <c r="R57" t="n">
-        <v>7024009</v>
+        <v>7023767</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7543,7 +7542,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I stubbe och låga av knäckt gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7552,6 +7551,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130180032</v>
+        <v>130180066</v>
       </c>
       <c r="B58" t="n">
-        <v>57826</v>
+        <v>79209</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7606,46 +7606,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490566</v>
+        <v>490497</v>
       </c>
       <c r="R58" t="n">
-        <v>7023832</v>
+        <v>7024012</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7682,7 +7670,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en smal gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7693,31 +7681,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7737,7 +7700,7 @@
         <v>130180076</v>
       </c>
       <c r="B59" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7836,10 +7799,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130180066</v>
+        <v>130180032</v>
       </c>
       <c r="B60" t="n">
-        <v>79183</v>
+        <v>57852</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7847,34 +7810,46 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490497</v>
+        <v>490566</v>
       </c>
       <c r="R60" t="n">
-        <v>7024012</v>
+        <v>7023832</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7911,7 +7886,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en smal gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7922,6 +7897,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130180017</v>
+        <v>130180041</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>58011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,42 +1021,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490478</v>
+        <v>490626</v>
       </c>
       <c r="R5" t="n">
-        <v>7024005</v>
+        <v>7023887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1101,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 1 individ, ev. fler. Fyndplatsen finns i flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,24 +1118,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1145,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130180041</v>
+        <v>130180017</v>
       </c>
       <c r="B6" t="n">
-        <v>58011</v>
+        <v>57852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,50 +1149,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490626</v>
+        <v>490478</v>
       </c>
       <c r="R6" t="n">
-        <v>7023887</v>
+        <v>7024005</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1221,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 1 individ, ev. fler. Fyndplatsen finns i flerskiktad äldre barrblandskog.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,9 +1238,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre barrblandskog.</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130180074</v>
+        <v>130180039</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,34 +1284,54 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490581</v>
+        <v>490650</v>
       </c>
       <c r="R7" t="n">
-        <v>7023945</v>
+        <v>7023840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1368,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,6 +1379,36 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1375,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130180039</v>
+        <v>130180074</v>
       </c>
       <c r="B8" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,54 +1436,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490650</v>
+        <v>490581</v>
       </c>
       <c r="R8" t="n">
-        <v>7023840</v>
+        <v>7023945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1500,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,36 +1511,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -4096,10 +4096,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130180033</v>
+        <v>130180009</v>
       </c>
       <c r="B29" t="n">
-        <v>57852</v>
+        <v>91757</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,29 +4107,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4139,10 +4138,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490591</v>
+        <v>490651</v>
       </c>
       <c r="R29" t="n">
-        <v>7023786</v>
+        <v>7024020</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4179,7 +4178,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I en granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4188,6 +4187,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4208,12 +4208,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130180072</v>
+        <v>130180008</v>
       </c>
       <c r="B30" t="n">
-        <v>79209</v>
+        <v>91757</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4242,34 +4242,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490590</v>
+        <v>490598</v>
       </c>
       <c r="R30" t="n">
-        <v>7023801</v>
+        <v>7023986</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4306,7 +4313,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>I granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4315,8 +4322,34 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4333,7 +4366,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130180069</v>
+        <v>130180072</v>
       </c>
       <c r="B31" t="n">
         <v>79209</v>
@@ -4368,10 +4401,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490566</v>
+        <v>490590</v>
       </c>
       <c r="R31" t="n">
-        <v>7023937</v>
+        <v>7023801</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4408,7 +4441,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4435,52 +4468,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180042</v>
+        <v>130180069</v>
       </c>
       <c r="B32" t="n">
-        <v>80343</v>
+        <v>79209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490679</v>
+        <v>490566</v>
       </c>
       <c r="R32" t="n">
-        <v>7023796</v>
+        <v>7023937</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4517,7 +4543,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4526,34 +4552,8 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4570,39 +4570,39 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130180009</v>
+        <v>130180042</v>
       </c>
       <c r="B33" t="n">
-        <v>91757</v>
+        <v>80343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490651</v>
+        <v>490679</v>
       </c>
       <c r="R33" t="n">
-        <v>7024020</v>
+        <v>7023796</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>I en granlåga i barrblandskog.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4672,22 +4672,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4705,10 +4705,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130180008</v>
+        <v>130180033</v>
       </c>
       <c r="B34" t="n">
-        <v>91757</v>
+        <v>57852</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4716,28 +4716,29 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4747,10 +4748,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490598</v>
+        <v>490591</v>
       </c>
       <c r="R34" t="n">
-        <v>7023986</v>
+        <v>7023786</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4787,7 +4788,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>I granlåga i barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4796,7 +4797,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130180037</v>
+        <v>130180060</v>
       </c>
       <c r="B46" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6142,42 +6142,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490575</v>
+        <v>490647</v>
       </c>
       <c r="R46" t="n">
-        <v>7023818</v>
+        <v>7023943</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6214,7 +6206,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6225,31 +6217,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6266,10 +6233,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130180060</v>
+        <v>130180037</v>
       </c>
       <c r="B47" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6277,34 +6244,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490647</v>
+        <v>490575</v>
       </c>
       <c r="R47" t="n">
-        <v>7023943</v>
+        <v>7023818</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6341,7 +6316,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6352,6 +6327,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130180015</v>
+        <v>130180052</v>
       </c>
       <c r="B56" t="n">
-        <v>57852</v>
+        <v>91777</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7340,29 +7340,24 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7372,10 +7367,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490474</v>
+        <v>490615</v>
       </c>
       <c r="R56" t="n">
-        <v>7024009</v>
+        <v>7023767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7412,7 +7407,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I stubbe och låga av knäckt gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7421,6 +7416,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7441,12 +7437,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7464,10 +7460,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130180052</v>
+        <v>130180015</v>
       </c>
       <c r="B57" t="n">
-        <v>91777</v>
+        <v>57852</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7475,24 +7471,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7502,10 +7503,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490615</v>
+        <v>490474</v>
       </c>
       <c r="R57" t="n">
-        <v>7023767</v>
+        <v>7024009</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7542,7 +7543,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>I stubbe och låga av knäckt gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7551,7 +7552,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130180041</v>
+        <v>130180017</v>
       </c>
       <c r="B5" t="n">
-        <v>58011</v>
+        <v>57852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,50 +1021,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490626</v>
+        <v>490478</v>
       </c>
       <c r="R5" t="n">
-        <v>7023887</v>
+        <v>7024005</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 1 individ, ev. fler. Fyndplatsen finns i flerskiktad äldre barrblandskog.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,9 +1110,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre barrblandskog.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1138,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130180017</v>
+        <v>130180041</v>
       </c>
       <c r="B6" t="n">
-        <v>57852</v>
+        <v>58011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,42 +1156,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490478</v>
+        <v>490626</v>
       </c>
       <c r="R6" t="n">
-        <v>7024005</v>
+        <v>7023887</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1236,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 1 individ, ev. fler. Fyndplatsen finns i flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,24 +1253,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130180039</v>
+        <v>130180074</v>
       </c>
       <c r="B7" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,54 +1284,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490650</v>
+        <v>490581</v>
       </c>
       <c r="R7" t="n">
-        <v>7023840</v>
+        <v>7023945</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1348,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,36 +1359,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1425,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130180074</v>
+        <v>130180039</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,34 +1386,54 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490581</v>
+        <v>490650</v>
       </c>
       <c r="R8" t="n">
-        <v>7023945</v>
+        <v>7023840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,6 +1481,36 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1764,10 +1764,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130180028</v>
+        <v>130180070</v>
       </c>
       <c r="B11" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,31 +1775,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490534</v>
+        <v>490547</v>
       </c>
       <c r="R11" t="n">
-        <v>7023897</v>
+        <v>7023925</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1847,7 +1842,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1856,6 +1851,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1876,12 +1872,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1899,7 +1895,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130180070</v>
+        <v>130180064</v>
       </c>
       <c r="B12" t="n">
         <v>79209</v>
@@ -1928,19 +1924,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490547</v>
+        <v>490655</v>
       </c>
       <c r="R12" t="n">
-        <v>7023925</v>
+        <v>7024022</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,7 +1970,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,34 +1979,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2030,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130180064</v>
+        <v>130180028</v>
       </c>
       <c r="B13" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,34 +2008,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490655</v>
+        <v>490534</v>
       </c>
       <c r="R13" t="n">
-        <v>7024022</v>
+        <v>7023897</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2105,7 +2080,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2116,6 +2091,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2132,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130180061</v>
+        <v>130180019</v>
       </c>
       <c r="B14" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,26 +2143,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2170,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490539</v>
+        <v>490488</v>
       </c>
       <c r="R14" t="n">
-        <v>7024036</v>
+        <v>7023990</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2210,7 +2215,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,7 +2224,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2240,12 +2244,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2263,7 +2267,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130180019</v>
+        <v>130180018</v>
       </c>
       <c r="B15" t="n">
         <v>57852</v>
@@ -2306,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490488</v>
+        <v>490478</v>
       </c>
       <c r="R15" t="n">
-        <v>7023990</v>
+        <v>7024001</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2398,10 +2402,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130180018</v>
+        <v>130180061</v>
       </c>
       <c r="B16" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,31 +2413,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2441,10 +2440,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490478</v>
+        <v>490539</v>
       </c>
       <c r="R16" t="n">
-        <v>7024001</v>
+        <v>7024036</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2481,7 +2480,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,6 +2489,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2536,7 +2536,7 @@
         <v>130180047</v>
       </c>
       <c r="B17" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130180020</v>
+        <v>130180051</v>
       </c>
       <c r="B21" t="n">
-        <v>57852</v>
+        <v>91778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3070,46 +3070,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490494</v>
+        <v>490648</v>
       </c>
       <c r="R21" t="n">
-        <v>7023983</v>
+        <v>7023846</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3146,7 +3137,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3155,6 +3146,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3163,6 +3155,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3175,12 +3172,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3198,10 +3195,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180014</v>
+        <v>130180078</v>
       </c>
       <c r="B22" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3209,42 +3206,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490533</v>
+        <v>490660</v>
       </c>
       <c r="R22" t="n">
-        <v>7024027</v>
+        <v>7023791</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3281,7 +3270,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3292,31 +3281,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3333,49 +3297,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130180046</v>
+        <v>130180020</v>
       </c>
       <c r="B23" t="n">
-        <v>97820</v>
+        <v>57852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490513</v>
+        <v>490494</v>
       </c>
       <c r="R23" t="n">
-        <v>7023984</v>
+        <v>7023983</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3412,7 +3384,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3421,13 +3393,32 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3445,10 +3436,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130180051</v>
+        <v>130180014</v>
       </c>
       <c r="B24" t="n">
-        <v>91777</v>
+        <v>57852</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3456,24 +3447,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3483,10 +3479,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490648</v>
+        <v>490533</v>
       </c>
       <c r="R24" t="n">
-        <v>7023846</v>
+        <v>7024027</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3523,7 +3519,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3532,7 +3528,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3541,11 +3536,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ24" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3558,12 +3548,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3581,45 +3571,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130180078</v>
+        <v>130180046</v>
       </c>
       <c r="B25" t="n">
-        <v>79209</v>
+        <v>97821</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490660</v>
+        <v>490513</v>
       </c>
       <c r="R25" t="n">
-        <v>7023791</v>
+        <v>7023984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3656,7 +3650,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3665,8 +3659,14 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -4099,7 +4099,7 @@
         <v>130180009</v>
       </c>
       <c r="B29" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>130180008</v>
       </c>
       <c r="B30" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130180072</v>
+        <v>130180069</v>
       </c>
       <c r="B31" t="n">
         <v>79209</v>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490590</v>
+        <v>490566</v>
       </c>
       <c r="R31" t="n">
-        <v>7023801</v>
+        <v>7023937</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4468,7 +4468,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180069</v>
+        <v>130180072</v>
       </c>
       <c r="B32" t="n">
         <v>79209</v>
@@ -4503,10 +4503,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490566</v>
+        <v>490590</v>
       </c>
       <c r="R32" t="n">
-        <v>7023937</v>
+        <v>7023801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4840,10 +4840,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130180059</v>
+        <v>130180025</v>
       </c>
       <c r="B35" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4851,34 +4851,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490614</v>
+        <v>490547</v>
       </c>
       <c r="R35" t="n">
-        <v>7023878</v>
+        <v>7023930</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4915,7 +4923,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4926,6 +4934,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4942,10 +4975,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130180063</v>
+        <v>130180027</v>
       </c>
       <c r="B36" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4953,34 +4986,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490561</v>
+        <v>490539</v>
       </c>
       <c r="R36" t="n">
-        <v>7023986</v>
+        <v>7023923</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5017,7 +5062,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5028,6 +5073,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5146,10 +5216,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130180016</v>
+        <v>130180059</v>
       </c>
       <c r="B38" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5157,42 +5227,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490471</v>
+        <v>490614</v>
       </c>
       <c r="R38" t="n">
-        <v>7024008</v>
+        <v>7023878</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5229,7 +5291,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5240,31 +5302,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5281,10 +5318,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130180025</v>
+        <v>130180063</v>
       </c>
       <c r="B39" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5292,42 +5329,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490547</v>
+        <v>490561</v>
       </c>
       <c r="R39" t="n">
-        <v>7023930</v>
+        <v>7023986</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5364,7 +5393,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5375,31 +5404,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5416,7 +5420,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130180035</v>
+        <v>130180016</v>
       </c>
       <c r="B40" t="n">
         <v>57852</v>
@@ -5459,10 +5463,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490603</v>
+        <v>490471</v>
       </c>
       <c r="R40" t="n">
-        <v>7023797</v>
+        <v>7024008</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5499,7 +5503,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
+          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5513,7 +5517,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5551,7 +5555,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130180034</v>
+        <v>130180035</v>
       </c>
       <c r="B41" t="n">
         <v>57852</v>
@@ -5594,10 +5598,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490609</v>
+        <v>490603</v>
       </c>
       <c r="R41" t="n">
-        <v>7023788</v>
+        <v>7023797</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5634,7 +5638,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5686,7 +5690,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130180027</v>
+        <v>130180034</v>
       </c>
       <c r="B42" t="n">
         <v>57852</v>
@@ -5722,21 +5726,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490539</v>
+        <v>490609</v>
       </c>
       <c r="R42" t="n">
-        <v>7023923</v>
+        <v>7023788</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
+          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5825,7 +5825,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130180077</v>
+        <v>130180068</v>
       </c>
       <c r="B43" t="n">
         <v>79209</v>
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490626</v>
+        <v>490541</v>
       </c>
       <c r="R43" t="n">
-        <v>7023902</v>
+        <v>7023968</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Enstaka på gran i äldre barrblandskog.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5927,7 +5927,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130180068</v>
+        <v>130180077</v>
       </c>
       <c r="B44" t="n">
         <v>79209</v>
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490541</v>
+        <v>490626</v>
       </c>
       <c r="R44" t="n">
-        <v>7023968</v>
+        <v>7023902</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>Enstaka på gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6029,10 +6029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130180062</v>
+        <v>130180037</v>
       </c>
       <c r="B45" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6040,34 +6040,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490550</v>
+        <v>490575</v>
       </c>
       <c r="R45" t="n">
-        <v>7023998</v>
+        <v>7023818</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6104,7 +6112,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6115,6 +6123,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6233,10 +6266,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130180037</v>
+        <v>130180062</v>
       </c>
       <c r="B47" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,42 +6277,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490575</v>
+        <v>490550</v>
       </c>
       <c r="R47" t="n">
-        <v>7023818</v>
+        <v>7023998</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6316,7 +6341,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6327,31 +6352,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6371,7 +6371,7 @@
         <v>130180045</v>
       </c>
       <c r="B48" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>130180044</v>
       </c>
       <c r="B55" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7329,10 +7329,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130180052</v>
+        <v>130180015</v>
       </c>
       <c r="B56" t="n">
-        <v>91777</v>
+        <v>57852</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7340,24 +7340,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7367,10 +7372,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490615</v>
+        <v>490474</v>
       </c>
       <c r="R56" t="n">
-        <v>7023767</v>
+        <v>7024009</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7407,7 +7412,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>I stubbe och låga av knäckt gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7416,7 +7421,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7437,12 +7441,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7460,10 +7464,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130180015</v>
+        <v>130180052</v>
       </c>
       <c r="B57" t="n">
-        <v>57852</v>
+        <v>91778</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7471,29 +7475,24 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7503,10 +7502,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490474</v>
+        <v>490615</v>
       </c>
       <c r="R57" t="n">
-        <v>7024009</v>
+        <v>7023767</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7543,7 +7542,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I stubbe och låga av knäckt gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7552,6 +7551,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7595,7 +7595,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130180066</v>
+        <v>130180076</v>
       </c>
       <c r="B58" t="n">
         <v>79209</v>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490497</v>
+        <v>490653</v>
       </c>
       <c r="R58" t="n">
-        <v>7024012</v>
+        <v>7023898</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran intill andra hänglavar, i barrblandskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7697,7 +7697,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130180076</v>
+        <v>130180066</v>
       </c>
       <c r="B59" t="n">
         <v>79209</v>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490653</v>
+        <v>490497</v>
       </c>
       <c r="R59" t="n">
-        <v>7023898</v>
+        <v>7024012</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gran intill andra hänglavar, i barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130180017</v>
+        <v>130180041</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>58011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,42 +1021,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490478</v>
+        <v>490626</v>
       </c>
       <c r="R5" t="n">
-        <v>7024005</v>
+        <v>7023887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1101,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 1 individ, ev. fler. Fyndplatsen finns i flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,24 +1118,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1145,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130180041</v>
+        <v>130180017</v>
       </c>
       <c r="B6" t="n">
-        <v>58011</v>
+        <v>57852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,50 +1149,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490626</v>
+        <v>490478</v>
       </c>
       <c r="R6" t="n">
-        <v>7023887</v>
+        <v>7024005</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1221,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 1 individ, ev. fler. Fyndplatsen finns i flerskiktad äldre barrblandskog.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,9 +1238,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre barrblandskog.</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130180071</v>
+        <v>130180021</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,34 +1538,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490541</v>
+        <v>490508</v>
       </c>
       <c r="R9" t="n">
-        <v>7023902</v>
+        <v>7023972</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1610,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en hyfsst grov gran en bit innanför en hyggeskant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,6 +1621,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1629,10 +1662,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130180021</v>
+        <v>130180071</v>
       </c>
       <c r="B10" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,42 +1673,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490508</v>
+        <v>490541</v>
       </c>
       <c r="R10" t="n">
-        <v>7023972</v>
+        <v>7023902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1737,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en hyfsst grov gran en bit innanför en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,31 +1748,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1764,10 +1764,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130180070</v>
+        <v>130180028</v>
       </c>
       <c r="B11" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,26 +1775,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490547</v>
+        <v>490534</v>
       </c>
       <c r="R11" t="n">
-        <v>7023925</v>
+        <v>7023897</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,7 +1847,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,7 +1856,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1872,12 +1876,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1895,7 +1899,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130180064</v>
+        <v>130180070</v>
       </c>
       <c r="B12" t="n">
         <v>79209</v>
@@ -1924,16 +1928,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490655</v>
+        <v>490547</v>
       </c>
       <c r="R12" t="n">
-        <v>7024022</v>
+        <v>7023925</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1970,7 +1977,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,8 +1986,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1997,10 +2030,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130180028</v>
+        <v>130180064</v>
       </c>
       <c r="B13" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,42 +2041,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490534</v>
+        <v>490655</v>
       </c>
       <c r="R13" t="n">
-        <v>7023897</v>
+        <v>7024022</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2080,7 +2105,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,31 +2116,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2536,7 +2536,7 @@
         <v>130180047</v>
       </c>
       <c r="B17" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130180038</v>
+        <v>130180023</v>
       </c>
       <c r="B18" t="n">
         <v>57852</v>
@@ -2678,24 +2678,20 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490648</v>
+        <v>490509</v>
       </c>
       <c r="R18" t="n">
-        <v>7023846</v>
+        <v>7023962</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2732,14 +2728,14 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gamla bohål i en stående död gran med full längd som har fruktkroppar av granticka. Ett bohål (diameter 4 cm) på 1,8 meters höjd, och ett bohål (diameter 4,5 cm) på 2,1 meters höjd. Finns även fler bohål och andra hackade hål högre upp i granstammen. Troligen bohål som tidigare använts av tretåig hackspett. Hålens storlek och att en hona av tretåig hackspett födosökte precis intill styrker detta.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
@@ -2749,11 +2745,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2766,12 +2757,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2789,7 +2780,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130180023</v>
+        <v>130180022</v>
       </c>
       <c r="B19" t="n">
         <v>57852</v>
@@ -2832,10 +2823,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490509</v>
+        <v>490522</v>
       </c>
       <c r="R19" t="n">
-        <v>7023962</v>
+        <v>7023957</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2872,7 +2863,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2924,7 +2915,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130180022</v>
+        <v>130180038</v>
       </c>
       <c r="B20" t="n">
         <v>57852</v>
@@ -2957,20 +2948,24 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490522</v>
+        <v>490648</v>
       </c>
       <c r="R20" t="n">
-        <v>7023957</v>
+        <v>7023846</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3007,14 +3002,14 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
+          <t>Gamla bohål i en stående död gran med full längd som har fruktkroppar av granticka. Ett bohål (diameter 4 cm) på 1,8 meters höjd, och ett bohål (diameter 4,5 cm) på 2,1 meters höjd. Finns även fler bohål och andra hackade hål högre upp i granstammen. Troligen bohål som tidigare använts av tretåig hackspett. Hålens storlek och att en hona av tretåig hackspett födosökte precis intill styrker detta.</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -3024,6 +3019,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3036,12 +3036,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130180051</v>
+        <v>130180014</v>
       </c>
       <c r="B21" t="n">
-        <v>91778</v>
+        <v>57852</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3070,24 +3070,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3097,10 +3102,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490648</v>
+        <v>490533</v>
       </c>
       <c r="R21" t="n">
-        <v>7023846</v>
+        <v>7024027</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3137,7 +3142,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3146,7 +3151,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3155,11 +3159,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3172,12 +3171,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3297,57 +3296,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130180020</v>
+        <v>130180046</v>
       </c>
       <c r="B23" t="n">
-        <v>57852</v>
+        <v>97822</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490494</v>
+        <v>490513</v>
       </c>
       <c r="R23" t="n">
-        <v>7023983</v>
+        <v>7023984</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3384,7 +3375,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3393,32 +3384,13 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3436,10 +3408,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130180014</v>
+        <v>130180051</v>
       </c>
       <c r="B24" t="n">
-        <v>57852</v>
+        <v>91779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3447,29 +3419,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3479,10 +3446,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490533</v>
+        <v>490648</v>
       </c>
       <c r="R24" t="n">
-        <v>7024027</v>
+        <v>7023846</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3519,7 +3486,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3528,6 +3495,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3536,6 +3504,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ24" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3548,12 +3521,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3571,49 +3544,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130180046</v>
+        <v>130180020</v>
       </c>
       <c r="B25" t="n">
-        <v>97821</v>
+        <v>57852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490513</v>
+        <v>490494</v>
       </c>
       <c r="R25" t="n">
-        <v>7023984</v>
+        <v>7023983</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3650,7 +3631,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3659,13 +3640,32 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4099,7 +4099,7 @@
         <v>130180009</v>
       </c>
       <c r="B29" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>130180008</v>
       </c>
       <c r="B30" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130180069</v>
+        <v>130180033</v>
       </c>
       <c r="B31" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4377,34 +4377,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490566</v>
+        <v>490591</v>
       </c>
       <c r="R31" t="n">
-        <v>7023937</v>
+        <v>7023786</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4441,7 +4449,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4452,6 +4460,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4468,7 +4501,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180072</v>
+        <v>130180069</v>
       </c>
       <c r="B32" t="n">
         <v>79209</v>
@@ -4503,10 +4536,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490590</v>
+        <v>490566</v>
       </c>
       <c r="R32" t="n">
-        <v>7023801</v>
+        <v>7023937</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4543,7 +4576,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4570,52 +4603,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130180042</v>
+        <v>130180072</v>
       </c>
       <c r="B33" t="n">
-        <v>80343</v>
+        <v>79209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490679</v>
+        <v>490590</v>
       </c>
       <c r="R33" t="n">
-        <v>7023796</v>
+        <v>7023801</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4652,7 +4678,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4661,34 +4687,8 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4705,40 +4705,39 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130180033</v>
+        <v>130180042</v>
       </c>
       <c r="B34" t="n">
-        <v>57852</v>
+        <v>80343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4748,10 +4747,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490591</v>
+        <v>490679</v>
       </c>
       <c r="R34" t="n">
-        <v>7023786</v>
+        <v>7023796</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4788,7 +4787,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4797,6 +4796,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4807,22 +4807,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130180025</v>
+        <v>130180065</v>
       </c>
       <c r="B35" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4851,42 +4851,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490547</v>
+        <v>490576</v>
       </c>
       <c r="R35" t="n">
-        <v>7023930</v>
+        <v>7023998</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4923,7 +4915,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4934,31 +4926,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4975,10 +4942,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130180027</v>
+        <v>130180059</v>
       </c>
       <c r="B36" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4986,46 +4953,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490539</v>
+        <v>490614</v>
       </c>
       <c r="R36" t="n">
-        <v>7023923</v>
+        <v>7023878</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5062,7 +5017,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5073,31 +5028,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5114,7 +5044,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130180065</v>
+        <v>130180063</v>
       </c>
       <c r="B37" t="n">
         <v>79209</v>
@@ -5149,10 +5079,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490576</v>
+        <v>490561</v>
       </c>
       <c r="R37" t="n">
-        <v>7023998</v>
+        <v>7023986</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5189,7 +5119,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5216,10 +5146,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130180059</v>
+        <v>130180025</v>
       </c>
       <c r="B38" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5227,34 +5157,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490614</v>
+        <v>490547</v>
       </c>
       <c r="R38" t="n">
-        <v>7023878</v>
+        <v>7023930</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5291,7 +5229,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5302,6 +5240,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5318,10 +5281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130180063</v>
+        <v>130180034</v>
       </c>
       <c r="B39" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5329,34 +5292,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490561</v>
+        <v>490609</v>
       </c>
       <c r="R39" t="n">
-        <v>7023986</v>
+        <v>7023788</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5393,7 +5364,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5404,6 +5375,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5420,7 +5416,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130180016</v>
+        <v>130180027</v>
       </c>
       <c r="B40" t="n">
         <v>57852</v>
@@ -5456,17 +5452,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490471</v>
+        <v>490539</v>
       </c>
       <c r="R40" t="n">
-        <v>7024008</v>
+        <v>7023923</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5555,7 +5555,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130180035</v>
+        <v>130180016</v>
       </c>
       <c r="B41" t="n">
         <v>57852</v>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490603</v>
+        <v>490471</v>
       </c>
       <c r="R41" t="n">
-        <v>7023797</v>
+        <v>7024008</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
+          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5690,7 +5690,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130180034</v>
+        <v>130180035</v>
       </c>
       <c r="B42" t="n">
         <v>57852</v>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490609</v>
+        <v>490603</v>
       </c>
       <c r="R42" t="n">
-        <v>7023788</v>
+        <v>7023797</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6029,10 +6029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130180037</v>
+        <v>130180060</v>
       </c>
       <c r="B45" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6040,42 +6040,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490575</v>
+        <v>490647</v>
       </c>
       <c r="R45" t="n">
-        <v>7023818</v>
+        <v>7023943</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6112,7 +6104,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6123,31 +6115,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6164,7 +6131,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130180060</v>
+        <v>130180062</v>
       </c>
       <c r="B46" t="n">
         <v>79209</v>
@@ -6199,10 +6166,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490647</v>
+        <v>490550</v>
       </c>
       <c r="R46" t="n">
-        <v>7023943</v>
+        <v>7023998</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6266,10 +6233,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130180062</v>
+        <v>130180037</v>
       </c>
       <c r="B47" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6277,34 +6244,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490550</v>
+        <v>490575</v>
       </c>
       <c r="R47" t="n">
-        <v>7023998</v>
+        <v>7023818</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6341,7 +6316,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6352,6 +6327,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6371,7 +6371,7 @@
         <v>130180045</v>
       </c>
       <c r="B48" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>130180044</v>
       </c>
       <c r="B55" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>130180052</v>
       </c>
       <c r="B57" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
         <v>130180040</v>
       </c>
       <c r="B3" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>130180073</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130180041</v>
+        <v>130180017</v>
       </c>
       <c r="B5" t="n">
-        <v>58011</v>
+        <v>57854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,50 +1021,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490626</v>
+        <v>490478</v>
       </c>
       <c r="R5" t="n">
-        <v>7023887</v>
+        <v>7024005</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 1 individ, ev. fler. Fyndplatsen finns i flerskiktad äldre barrblandskog.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,9 +1110,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre barrblandskog.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1138,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130180017</v>
+        <v>130180041</v>
       </c>
       <c r="B6" t="n">
-        <v>57852</v>
+        <v>58013</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,42 +1156,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490478</v>
+        <v>490626</v>
       </c>
       <c r="R6" t="n">
-        <v>7024005</v>
+        <v>7023887</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1236,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 1 individ, ev. fler. Fyndplatsen finns i flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,24 +1253,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1276,7 +1276,7 @@
         <v>130180074</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>130180039</v>
       </c>
       <c r="B8" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1527,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130180021</v>
+        <v>130180071</v>
       </c>
       <c r="B9" t="n">
-        <v>57852</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,42 +1538,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490508</v>
+        <v>490541</v>
       </c>
       <c r="R9" t="n">
-        <v>7023972</v>
+        <v>7023902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1610,7 +1602,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en hyfsst grov gran en bit innanför en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,31 +1613,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1662,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130180071</v>
+        <v>130180021</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>57854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,34 +1640,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490541</v>
+        <v>490508</v>
       </c>
       <c r="R10" t="n">
-        <v>7023902</v>
+        <v>7023972</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1737,7 +1712,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en hyfsst grov gran en bit innanför en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,6 +1723,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1764,10 +1764,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130180028</v>
+        <v>130180070</v>
       </c>
       <c r="B11" t="n">
-        <v>57852</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,31 +1775,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490534</v>
+        <v>490547</v>
       </c>
       <c r="R11" t="n">
-        <v>7023897</v>
+        <v>7023925</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1847,7 +1842,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1856,6 +1851,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1876,12 +1872,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1899,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130180070</v>
+        <v>130180064</v>
       </c>
       <c r="B12" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,19 +1924,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490547</v>
+        <v>490655</v>
       </c>
       <c r="R12" t="n">
-        <v>7023925</v>
+        <v>7024022</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,7 +1970,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,34 +1979,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2030,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130180064</v>
+        <v>130180028</v>
       </c>
       <c r="B13" t="n">
-        <v>79209</v>
+        <v>57854</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,34 +2008,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490655</v>
+        <v>490534</v>
       </c>
       <c r="R13" t="n">
-        <v>7024022</v>
+        <v>7023897</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2105,7 +2080,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2116,6 +2091,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2132,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130180019</v>
+        <v>130180061</v>
       </c>
       <c r="B14" t="n">
-        <v>57852</v>
+        <v>79211</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,31 +2143,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2175,10 +2170,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490488</v>
+        <v>490539</v>
       </c>
       <c r="R14" t="n">
-        <v>7023990</v>
+        <v>7024036</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2215,7 +2210,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,6 +2219,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2244,12 +2240,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2267,10 +2263,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130180018</v>
+        <v>130180019</v>
       </c>
       <c r="B15" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,10 +2306,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490478</v>
+        <v>490488</v>
       </c>
       <c r="R15" t="n">
-        <v>7024001</v>
+        <v>7023990</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2402,10 +2398,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130180061</v>
+        <v>130180018</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>57854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,26 +2409,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2440,10 +2441,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490539</v>
+        <v>490478</v>
       </c>
       <c r="R16" t="n">
-        <v>7024036</v>
+        <v>7024001</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2480,7 +2481,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,7 +2490,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2536,7 +2536,7 @@
         <v>130180047</v>
       </c>
       <c r="B17" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130180023</v>
+        <v>130180038</v>
       </c>
       <c r="B18" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2678,20 +2678,24 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490509</v>
+        <v>490648</v>
       </c>
       <c r="R18" t="n">
-        <v>7023962</v>
+        <v>7023846</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2728,14 +2732,14 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Gamla bohål i en stående död gran med full längd som har fruktkroppar av granticka. Ett bohål (diameter 4 cm) på 1,8 meters höjd, och ett bohål (diameter 4,5 cm) på 2,1 meters höjd. Finns även fler bohål och andra hackade hål högre upp i granstammen. Troligen bohål som tidigare använts av tretåig hackspett. Hålens storlek och att en hona av tretåig hackspett födosökte precis intill styrker detta.</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
@@ -2745,6 +2749,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2757,12 +2766,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2780,10 +2789,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130180022</v>
+        <v>130180023</v>
       </c>
       <c r="B19" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2823,10 +2832,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490522</v>
+        <v>490509</v>
       </c>
       <c r="R19" t="n">
-        <v>7023957</v>
+        <v>7023962</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2863,7 +2872,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2915,10 +2924,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130180038</v>
+        <v>130180022</v>
       </c>
       <c r="B20" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2948,24 +2957,20 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490648</v>
+        <v>490522</v>
       </c>
       <c r="R20" t="n">
-        <v>7023846</v>
+        <v>7023957</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3002,14 +3007,14 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gamla bohål i en stående död gran med full längd som har fruktkroppar av granticka. Ett bohål (diameter 4 cm) på 1,8 meters höjd, och ett bohål (diameter 4,5 cm) på 2,1 meters höjd. Finns även fler bohål och andra hackade hål högre upp i granstammen. Troligen bohål som tidigare använts av tretåig hackspett. Hålens storlek och att en hona av tretåig hackspett födosökte precis intill styrker detta.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -3019,11 +3024,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3036,12 +3036,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130180014</v>
+        <v>130180078</v>
       </c>
       <c r="B21" t="n">
-        <v>57852</v>
+        <v>79211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3070,42 +3070,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490533</v>
+        <v>490660</v>
       </c>
       <c r="R21" t="n">
-        <v>7024027</v>
+        <v>7023791</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3142,7 +3134,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3153,31 +3145,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3194,10 +3161,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180078</v>
+        <v>130180051</v>
       </c>
       <c r="B22" t="n">
-        <v>79209</v>
+        <v>91781</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3205,34 +3172,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490660</v>
+        <v>490648</v>
       </c>
       <c r="R22" t="n">
-        <v>7023791</v>
+        <v>7023846</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3269,7 +3239,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3278,8 +3248,39 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3296,49 +3297,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130180046</v>
+        <v>130180020</v>
       </c>
       <c r="B23" t="n">
-        <v>97822</v>
+        <v>57854</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490513</v>
+        <v>490494</v>
       </c>
       <c r="R23" t="n">
-        <v>7023984</v>
+        <v>7023983</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3375,7 +3384,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3384,13 +3393,32 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3408,10 +3436,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130180051</v>
+        <v>130180014</v>
       </c>
       <c r="B24" t="n">
-        <v>91779</v>
+        <v>57854</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3419,24 +3447,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3446,10 +3479,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490648</v>
+        <v>490533</v>
       </c>
       <c r="R24" t="n">
-        <v>7023846</v>
+        <v>7024027</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3486,7 +3519,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3495,7 +3528,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3504,11 +3536,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ24" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3521,12 +3548,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3544,57 +3571,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130180020</v>
+        <v>130180046</v>
       </c>
       <c r="B25" t="n">
-        <v>57852</v>
+        <v>97824</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490494</v>
+        <v>490513</v>
       </c>
       <c r="R25" t="n">
-        <v>7023983</v>
+        <v>7023984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3631,7 +3650,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3640,32 +3659,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3686,7 +3686,7 @@
         <v>130180036</v>
       </c>
       <c r="B26" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>130180031</v>
       </c>
       <c r="B27" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>130180029</v>
       </c>
       <c r="B28" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>130180009</v>
       </c>
       <c r="B29" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>130180008</v>
       </c>
       <c r="B30" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130180033</v>
+        <v>130180069</v>
       </c>
       <c r="B31" t="n">
-        <v>57852</v>
+        <v>79211</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4377,42 +4377,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490591</v>
+        <v>490566</v>
       </c>
       <c r="R31" t="n">
-        <v>7023786</v>
+        <v>7023937</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4449,7 +4441,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4460,31 +4452,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4501,10 +4468,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180069</v>
+        <v>130180072</v>
       </c>
       <c r="B32" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4536,10 +4503,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490566</v>
+        <v>490590</v>
       </c>
       <c r="R32" t="n">
-        <v>7023937</v>
+        <v>7023801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4576,7 +4543,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4603,10 +4570,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130180072</v>
+        <v>130180033</v>
       </c>
       <c r="B33" t="n">
-        <v>79209</v>
+        <v>57854</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4614,34 +4581,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490590</v>
+        <v>490591</v>
       </c>
       <c r="R33" t="n">
-        <v>7023801</v>
+        <v>7023786</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4678,7 +4653,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4689,6 +4664,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4708,7 +4708,7 @@
         <v>130180042</v>
       </c>
       <c r="B34" t="n">
-        <v>80343</v>
+        <v>80345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>130180065</v>
       </c>
       <c r="B35" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>130180059</v>
       </c>
       <c r="B36" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>130180063</v>
       </c>
       <c r="B37" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5146,10 +5146,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130180025</v>
+        <v>130180016</v>
       </c>
       <c r="B38" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490547</v>
+        <v>490471</v>
       </c>
       <c r="R38" t="n">
-        <v>7023930</v>
+        <v>7024008</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5281,10 +5281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130180034</v>
+        <v>130180025</v>
       </c>
       <c r="B39" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490609</v>
+        <v>490547</v>
       </c>
       <c r="R39" t="n">
-        <v>7023788</v>
+        <v>7023930</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5416,10 +5416,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130180027</v>
+        <v>130180035</v>
       </c>
       <c r="B40" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5452,21 +5452,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490539</v>
+        <v>490603</v>
       </c>
       <c r="R40" t="n">
-        <v>7023923</v>
+        <v>7023797</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5503,7 +5499,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
+          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5555,10 +5551,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130180016</v>
+        <v>130180034</v>
       </c>
       <c r="B41" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5598,10 +5594,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490471</v>
+        <v>490609</v>
       </c>
       <c r="R41" t="n">
-        <v>7024008</v>
+        <v>7023788</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5638,7 +5634,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5652,7 +5648,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5690,10 +5686,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130180035</v>
+        <v>130180027</v>
       </c>
       <c r="B42" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5726,17 +5722,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490603</v>
+        <v>490539</v>
       </c>
       <c r="R42" t="n">
-        <v>7023797</v>
+        <v>7023923</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
+          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5828,7 +5828,7 @@
         <v>130180068</v>
       </c>
       <c r="B43" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>130180077</v>
       </c>
       <c r="B44" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>130180060</v>
       </c>
       <c r="B45" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>130180062</v>
       </c>
       <c r="B46" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>130180037</v>
       </c>
       <c r="B47" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>130180045</v>
       </c>
       <c r="B48" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130180075</v>
+        <v>130180067</v>
       </c>
       <c r="B49" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490602</v>
+        <v>490505</v>
       </c>
       <c r="R49" t="n">
-        <v>7023937</v>
+        <v>7023981</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6582,10 +6582,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130180067</v>
+        <v>130180043</v>
       </c>
       <c r="B50" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6593,34 +6593,50 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490505</v>
+        <v>490588</v>
       </c>
       <c r="R50" t="n">
-        <v>7023981</v>
+        <v>7023887</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6657,7 +6673,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>1 individ med lockläte hördes här i skogen. En bit längre bort hördes en annan individ av spillkråka.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6668,6 +6684,16 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med gott om stående död ved.</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6684,10 +6710,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130180043</v>
+        <v>130180075</v>
       </c>
       <c r="B51" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6695,50 +6721,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490588</v>
+        <v>490602</v>
       </c>
       <c r="R51" t="n">
-        <v>7023887</v>
+        <v>7023937</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6775,7 +6785,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>1 individ med lockläte hördes här i skogen. En bit längre bort hördes en annan individ av spillkråka.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6786,16 +6796,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med gott om stående död ved.</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6815,7 +6815,7 @@
         <v>130180026</v>
       </c>
       <c r="B52" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>130180030</v>
       </c>
       <c r="B53" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>130180024</v>
       </c>
       <c r="B54" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>130180044</v>
       </c>
       <c r="B55" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7329,10 +7329,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130180015</v>
+        <v>130180052</v>
       </c>
       <c r="B56" t="n">
-        <v>57852</v>
+        <v>91781</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7340,29 +7340,24 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7372,10 +7367,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490474</v>
+        <v>490615</v>
       </c>
       <c r="R56" t="n">
-        <v>7024009</v>
+        <v>7023767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7412,7 +7407,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I stubbe och låga av knäckt gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7421,6 +7416,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7441,12 +7437,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7464,10 +7460,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130180052</v>
+        <v>130180015</v>
       </c>
       <c r="B57" t="n">
-        <v>91779</v>
+        <v>57854</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7475,24 +7471,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7502,10 +7503,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490615</v>
+        <v>490474</v>
       </c>
       <c r="R57" t="n">
-        <v>7023767</v>
+        <v>7024009</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7542,7 +7543,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>I stubbe och låga av knäckt gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7551,7 +7552,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7598,7 +7598,7 @@
         <v>130180076</v>
       </c>
       <c r="B58" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>130180066</v>
       </c>
       <c r="B59" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>130180032</v>
       </c>
       <c r="B60" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -1527,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130180071</v>
+        <v>130180021</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,34 +1538,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490541</v>
+        <v>490508</v>
       </c>
       <c r="R9" t="n">
-        <v>7023902</v>
+        <v>7023972</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1610,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en hyfsst grov gran en bit innanför en hyggeskant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,6 +1621,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1629,10 +1662,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130180021</v>
+        <v>130180071</v>
       </c>
       <c r="B10" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,42 +1673,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490508</v>
+        <v>490541</v>
       </c>
       <c r="R10" t="n">
-        <v>7023972</v>
+        <v>7023902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1737,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en hyfsst grov gran en bit innanför en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,31 +1748,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -2536,7 +2536,7 @@
         <v>130180047</v>
       </c>
       <c r="B17" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130180078</v>
+        <v>130180020</v>
       </c>
       <c r="B21" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3070,34 +3070,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490660</v>
+        <v>490494</v>
       </c>
       <c r="R21" t="n">
-        <v>7023791</v>
+        <v>7023983</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3134,7 +3146,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3145,6 +3157,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3161,10 +3198,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180051</v>
+        <v>130180078</v>
       </c>
       <c r="B22" t="n">
-        <v>91781</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3172,37 +3209,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490648</v>
+        <v>490660</v>
       </c>
       <c r="R22" t="n">
-        <v>7023846</v>
+        <v>7023791</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3239,7 +3273,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3248,39 +3282,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3297,10 +3300,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130180020</v>
+        <v>130180051</v>
       </c>
       <c r="B23" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3308,46 +3311,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490494</v>
+        <v>490648</v>
       </c>
       <c r="R23" t="n">
-        <v>7023983</v>
+        <v>7023846</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3384,7 +3378,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3393,6 +3387,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3401,6 +3396,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3413,12 +3413,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3574,7 +3574,7 @@
         <v>130180046</v>
       </c>
       <c r="B25" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130180009</v>
+        <v>130180008</v>
       </c>
       <c r="B29" t="n">
         <v>91761</v>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490651</v>
+        <v>490598</v>
       </c>
       <c r="R29" t="n">
-        <v>7024020</v>
+        <v>7023986</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I en granlåga i barrblandskog.</t>
+          <t>I granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4231,10 +4231,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130180008</v>
+        <v>130180072</v>
       </c>
       <c r="B30" t="n">
-        <v>91761</v>
+        <v>79211</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4242,41 +4242,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490598</v>
+        <v>490590</v>
       </c>
       <c r="R30" t="n">
-        <v>7023986</v>
+        <v>7023801</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4313,7 +4306,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>I granlåga i barrblandskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4322,34 +4315,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4468,45 +4435,52 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180072</v>
+        <v>130180042</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>80345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490590</v>
+        <v>490679</v>
       </c>
       <c r="R32" t="n">
-        <v>7023801</v>
+        <v>7023796</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4543,7 +4517,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4552,8 +4526,34 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4705,39 +4705,39 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130180042</v>
+        <v>130180009</v>
       </c>
       <c r="B34" t="n">
-        <v>80345</v>
+        <v>91761</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490679</v>
+        <v>490651</v>
       </c>
       <c r="R34" t="n">
-        <v>7023796</v>
+        <v>7024020</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>I en granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4807,22 +4807,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130180065</v>
+        <v>130180027</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4851,34 +4851,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490576</v>
+        <v>490539</v>
       </c>
       <c r="R35" t="n">
-        <v>7023998</v>
+        <v>7023923</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4915,7 +4927,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4926,6 +4938,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -5146,10 +5183,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130180016</v>
+        <v>130180065</v>
       </c>
       <c r="B38" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5157,42 +5194,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490471</v>
+        <v>490576</v>
       </c>
       <c r="R38" t="n">
-        <v>7024008</v>
+        <v>7023998</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5229,7 +5258,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5240,31 +5269,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5281,7 +5285,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130180025</v>
+        <v>130180016</v>
       </c>
       <c r="B39" t="n">
         <v>57854</v>
@@ -5324,10 +5328,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490547</v>
+        <v>490471</v>
       </c>
       <c r="R39" t="n">
-        <v>7023930</v>
+        <v>7024008</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5364,7 +5368,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5378,7 +5382,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5416,7 +5420,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130180035</v>
+        <v>130180025</v>
       </c>
       <c r="B40" t="n">
         <v>57854</v>
@@ -5459,10 +5463,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490603</v>
+        <v>490547</v>
       </c>
       <c r="R40" t="n">
-        <v>7023797</v>
+        <v>7023930</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5499,7 +5503,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5551,7 +5555,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130180034</v>
+        <v>130180035</v>
       </c>
       <c r="B41" t="n">
         <v>57854</v>
@@ -5594,10 +5598,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490609</v>
+        <v>490603</v>
       </c>
       <c r="R41" t="n">
-        <v>7023788</v>
+        <v>7023797</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5634,7 +5638,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5686,7 +5690,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130180027</v>
+        <v>130180034</v>
       </c>
       <c r="B42" t="n">
         <v>57854</v>
@@ -5722,21 +5726,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490539</v>
+        <v>490609</v>
       </c>
       <c r="R42" t="n">
-        <v>7023923</v>
+        <v>7023788</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
+          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5825,7 +5825,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130180068</v>
+        <v>130180077</v>
       </c>
       <c r="B43" t="n">
         <v>79211</v>
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490541</v>
+        <v>490626</v>
       </c>
       <c r="R43" t="n">
-        <v>7023968</v>
+        <v>7023902</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>Enstaka på gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5927,7 +5927,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130180077</v>
+        <v>130180068</v>
       </c>
       <c r="B44" t="n">
         <v>79211</v>
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490626</v>
+        <v>490541</v>
       </c>
       <c r="R44" t="n">
-        <v>7023902</v>
+        <v>7023968</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Enstaka på gran i äldre barrblandskog.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6029,7 +6029,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130180060</v>
+        <v>130180062</v>
       </c>
       <c r="B45" t="n">
         <v>79211</v>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490647</v>
+        <v>490550</v>
       </c>
       <c r="R45" t="n">
-        <v>7023943</v>
+        <v>7023998</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6131,7 +6131,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130180062</v>
+        <v>130180060</v>
       </c>
       <c r="B46" t="n">
         <v>79211</v>
@@ -6166,10 +6166,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490550</v>
+        <v>490647</v>
       </c>
       <c r="R46" t="n">
-        <v>7023998</v>
+        <v>7023943</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
         <v>130180045</v>
       </c>
       <c r="B48" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130180067</v>
+        <v>130180075</v>
       </c>
       <c r="B49" t="n">
         <v>79211</v>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490505</v>
+        <v>490602</v>
       </c>
       <c r="R49" t="n">
-        <v>7023981</v>
+        <v>7023937</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6582,10 +6582,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130180043</v>
+        <v>130180067</v>
       </c>
       <c r="B50" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6593,50 +6593,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490588</v>
+        <v>490505</v>
       </c>
       <c r="R50" t="n">
-        <v>7023887</v>
+        <v>7023981</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6673,7 +6657,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>1 individ med lockläte hördes här i skogen. En bit längre bort hördes en annan individ av spillkråka.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6684,16 +6668,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med gott om stående död ved.</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6710,10 +6684,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130180075</v>
+        <v>130180026</v>
       </c>
       <c r="B51" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6721,34 +6695,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490602</v>
+        <v>490539</v>
       </c>
       <c r="R51" t="n">
-        <v>7023937</v>
+        <v>7023926</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6785,7 +6767,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6796,6 +6778,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6812,10 +6819,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130180026</v>
+        <v>130180043</v>
       </c>
       <c r="B52" t="n">
-        <v>57854</v>
+        <v>57851</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6823,16 +6830,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6840,25 +6847,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490539</v>
+        <v>490588</v>
       </c>
       <c r="R52" t="n">
-        <v>7023926</v>
+        <v>7023887</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6895,7 +6910,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>1 individ med lockläte hördes här i skogen. En bit längre bort hördes en annan individ av spillkråka.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6912,24 +6927,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med gott om stående död ved.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6947,42 +6947,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130180030</v>
+        <v>130180044</v>
       </c>
       <c r="B53" t="n">
-        <v>57854</v>
+        <v>97828</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6990,10 +6986,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490538</v>
+        <v>490663</v>
       </c>
       <c r="R53" t="n">
-        <v>7023883</v>
+        <v>7024019</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7030,7 +7026,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7039,32 +7035,13 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7082,7 +7059,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130180024</v>
+        <v>130180030</v>
       </c>
       <c r="B54" t="n">
         <v>57854</v>
@@ -7125,10 +7102,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490550</v>
+        <v>490538</v>
       </c>
       <c r="R54" t="n">
-        <v>7023952</v>
+        <v>7023883</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7165,7 +7142,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid körspår.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7217,38 +7194,42 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130180044</v>
+        <v>130180024</v>
       </c>
       <c r="B55" t="n">
-        <v>97824</v>
+        <v>57854</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7256,10 +7237,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490663</v>
+        <v>490550</v>
       </c>
       <c r="R55" t="n">
-        <v>7024019</v>
+        <v>7023952</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7296,7 +7277,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid körspår.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7305,13 +7286,32 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130180076</v>
+        <v>130180032</v>
       </c>
       <c r="B58" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7606,34 +7606,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490653</v>
+        <v>490566</v>
       </c>
       <c r="R58" t="n">
-        <v>7023898</v>
+        <v>7023832</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7670,7 +7682,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gran intill andra hänglavar, i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en smal gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7681,6 +7693,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7799,10 +7836,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130180032</v>
+        <v>130180076</v>
       </c>
       <c r="B60" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7810,46 +7847,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490566</v>
+        <v>490653</v>
       </c>
       <c r="R60" t="n">
-        <v>7023832</v>
+        <v>7023898</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7886,7 +7911,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en smal gran vid en hyggeskant.</t>
+          <t>På gran intill andra hänglavar, i barrblandskog.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7897,31 +7922,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113248399</v>
+        <v>130180008</v>
       </c>
       <c r="B2" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Höglunda (Höglunda), Jmt</t>
+          <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490633</v>
+        <v>490598</v>
       </c>
       <c r="R2" t="n">
-        <v>7023994</v>
+        <v>7023986</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,12 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,28 +766,54 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130180040</v>
+        <v>130180009</v>
       </c>
       <c r="B3" t="n">
-        <v>57854</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,29 +821,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -821,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490609</v>
+        <v>490651</v>
       </c>
       <c r="R3" t="n">
-        <v>7023756</v>
+        <v>7024020</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid gammal hyggeskant.</t>
+          <t>I en granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,6 +901,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,9 +920,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -908,14 +945,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130180073</v>
+        <v>130180059</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -943,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490600</v>
+        <v>490614</v>
       </c>
       <c r="R4" t="n">
-        <v>7023920</v>
+        <v>7023878</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +1020,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,53 +1047,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130180017</v>
+        <v>130180060</v>
       </c>
       <c r="B5" t="n">
-        <v>57854</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490478</v>
+        <v>490647</v>
       </c>
       <c r="R5" t="n">
-        <v>7024005</v>
+        <v>7023943</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1122,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,31 +1133,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1145,61 +1149,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130180041</v>
+        <v>130180061</v>
       </c>
       <c r="B6" t="n">
-        <v>58013</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490626</v>
+        <v>490539</v>
       </c>
       <c r="R6" t="n">
-        <v>7023887</v>
+        <v>7024036</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1227,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 1 individ, ev. fler. Fyndplatsen finns i flerskiktad äldre barrblandskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,6 +1236,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1253,9 +1245,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre barrblandskog.</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1273,14 +1280,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130180074</v>
+        <v>130180062</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1308,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490581</v>
+        <v>490550</v>
       </c>
       <c r="R7" t="n">
-        <v>7023945</v>
+        <v>7023998</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,65 +1382,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130180039</v>
+        <v>130180063</v>
       </c>
       <c r="B8" t="n">
-        <v>57854</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490650</v>
+        <v>490561</v>
       </c>
       <c r="R8" t="n">
-        <v>7023840</v>
+        <v>7023986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1457,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,36 +1468,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1527,53 +1484,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130180021</v>
+        <v>130180064</v>
       </c>
       <c r="B9" t="n">
-        <v>57854</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490508</v>
+        <v>490655</v>
       </c>
       <c r="R9" t="n">
-        <v>7023972</v>
+        <v>7024022</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1610,7 +1559,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en hyfsst grov gran en bit innanför en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,31 +1570,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1662,14 +1586,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130180071</v>
+        <v>130180065</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1697,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490541</v>
+        <v>490576</v>
       </c>
       <c r="R10" t="n">
-        <v>7023902</v>
+        <v>7023998</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1737,7 +1661,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,14 +1688,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130180070</v>
+        <v>130180066</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1793,19 +1717,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490547</v>
+        <v>490497</v>
       </c>
       <c r="R11" t="n">
-        <v>7023925</v>
+        <v>7024012</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,7 +1763,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,34 +1772,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1895,14 +1790,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130180064</v>
+        <v>130180067</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1930,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490655</v>
+        <v>490505</v>
       </c>
       <c r="R12" t="n">
-        <v>7024022</v>
+        <v>7023981</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1970,7 +1865,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1997,53 +1892,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130180028</v>
+        <v>130180068</v>
       </c>
       <c r="B13" t="n">
-        <v>57854</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490534</v>
+        <v>490541</v>
       </c>
       <c r="R13" t="n">
-        <v>7023897</v>
+        <v>7023968</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2080,7 +1967,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,31 +1978,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2132,14 +1994,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130180061</v>
+        <v>130180069</v>
       </c>
       <c r="B14" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2161,19 +2023,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490539</v>
+        <v>490566</v>
       </c>
       <c r="R14" t="n">
-        <v>7024036</v>
+        <v>7023937</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2210,7 +2069,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,34 +2078,8 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2263,42 +2096,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130180019</v>
+        <v>130180070</v>
       </c>
       <c r="B15" t="n">
-        <v>57854</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2306,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490488</v>
+        <v>490547</v>
       </c>
       <c r="R15" t="n">
-        <v>7023990</v>
+        <v>7023925</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2174,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2355,6 +2183,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2375,12 +2204,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2398,53 +2227,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130180018</v>
+        <v>130180071</v>
       </c>
       <c r="B16" t="n">
-        <v>57854</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490478</v>
+        <v>490541</v>
       </c>
       <c r="R16" t="n">
-        <v>7024001</v>
+        <v>7023902</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2481,7 +2302,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2492,31 +2313,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2533,49 +2329,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130180047</v>
+        <v>130180072</v>
       </c>
       <c r="B17" t="n">
-        <v>97828</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490586</v>
+        <v>490590</v>
       </c>
       <c r="R17" t="n">
-        <v>7023926</v>
+        <v>7023801</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2612,7 +2404,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2621,14 +2413,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2645,57 +2431,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130180038</v>
+        <v>130180073</v>
       </c>
       <c r="B18" t="n">
-        <v>57854</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490648</v>
+        <v>490600</v>
       </c>
       <c r="R18" t="n">
-        <v>7023846</v>
+        <v>7023920</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2732,47 +2506,17 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gamla bohål i en stående död gran med full längd som har fruktkroppar av granticka. Ett bohål (diameter 4 cm) på 1,8 meters höjd, och ett bohål (diameter 4,5 cm) på 2,1 meters höjd. Finns även fler bohål och andra hackade hål högre upp i granstammen. Troligen bohål som tidigare använts av tretåig hackspett. Hålens storlek och att en hona av tretåig hackspett födosökte precis intill styrker detta.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2789,53 +2533,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130180023</v>
+        <v>130180074</v>
       </c>
       <c r="B19" t="n">
-        <v>57854</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490509</v>
+        <v>490581</v>
       </c>
       <c r="R19" t="n">
-        <v>7023962</v>
+        <v>7023945</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2872,7 +2608,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2883,31 +2619,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2924,53 +2635,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130180022</v>
+        <v>130180075</v>
       </c>
       <c r="B20" t="n">
-        <v>57854</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490522</v>
+        <v>490602</v>
       </c>
       <c r="R20" t="n">
-        <v>7023957</v>
+        <v>7023937</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3007,7 +2710,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
+          <t>På gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3018,31 +2721,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3059,57 +2737,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130180020</v>
+        <v>130180076</v>
       </c>
       <c r="B21" t="n">
-        <v>57854</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490494</v>
+        <v>490653</v>
       </c>
       <c r="R21" t="n">
-        <v>7023983</v>
+        <v>7023898</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3146,7 +2812,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
+          <t>På gran intill andra hänglavar, i barrblandskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3157,31 +2823,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3198,14 +2839,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130180078</v>
+        <v>130180077</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3233,10 +2874,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490660</v>
+        <v>490626</v>
       </c>
       <c r="R22" t="n">
-        <v>7023791</v>
+        <v>7023902</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3273,7 +2914,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Enstaka på gran i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3300,48 +2941,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130180051</v>
+        <v>130180078</v>
       </c>
       <c r="B23" t="n">
-        <v>91781</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490648</v>
+        <v>490660</v>
       </c>
       <c r="R23" t="n">
-        <v>7023846</v>
+        <v>7023791</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3378,7 +3016,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och bohål troligen efter tretåig hackspett.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3387,39 +3025,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3436,40 +3043,39 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130180014</v>
+        <v>130180042</v>
       </c>
       <c r="B24" t="n">
-        <v>57854</v>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3479,10 +3085,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490533</v>
+        <v>490679</v>
       </c>
       <c r="R24" t="n">
-        <v>7024027</v>
+        <v>7023796</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3519,7 +3125,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3528,6 +3134,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3538,22 +3145,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3571,10 +3178,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130180046</v>
+        <v>130180043</v>
       </c>
       <c r="B25" t="n">
-        <v>97828</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3582,38 +3189,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490513</v>
+        <v>490588</v>
       </c>
       <c r="R25" t="n">
-        <v>7023984</v>
+        <v>7023887</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3650,7 +3269,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>1 individ med lockläte hördes här i skogen. En bit längre bort hördes en annan individ av spillkråka.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3659,13 +3278,17 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med gott om stående död ved.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3683,10 +3306,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130180036</v>
+        <v>130180014</v>
       </c>
       <c r="B26" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3716,7 +3339,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3726,10 +3349,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490589</v>
+        <v>490533</v>
       </c>
       <c r="R26" t="n">
-        <v>7023793</v>
+        <v>7024027</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3766,7 +3389,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran inbäddad bland andra granar i en mer tät trädställning.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3780,7 +3403,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3818,10 +3441,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130180031</v>
+        <v>130180015</v>
       </c>
       <c r="B27" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3851,24 +3474,20 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490546</v>
+        <v>490474</v>
       </c>
       <c r="R27" t="n">
-        <v>7023885</v>
+        <v>7024009</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3905,7 +3524,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3957,10 +3576,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130180029</v>
+        <v>130180016</v>
       </c>
       <c r="B28" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3993,21 +3612,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490543</v>
+        <v>490471</v>
       </c>
       <c r="R28" t="n">
-        <v>7023888</v>
+        <v>7024008</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4044,7 +3659,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, i god mängd på en gran vid en hyggeskant. Troligen  skapade 2025.</t>
+          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4058,7 +3673,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4096,10 +3711,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130180008</v>
+        <v>130180017</v>
       </c>
       <c r="B29" t="n">
-        <v>91761</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,28 +3722,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4138,10 +3754,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490598</v>
+        <v>490478</v>
       </c>
       <c r="R29" t="n">
-        <v>7023986</v>
+        <v>7024005</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4178,7 +3794,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I granlåga i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4187,7 +3803,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4208,12 +3823,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4231,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130180072</v>
+        <v>130180018</v>
       </c>
       <c r="B30" t="n">
-        <v>79211</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4242,34 +3857,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490590</v>
+        <v>490478</v>
       </c>
       <c r="R30" t="n">
-        <v>7023801</v>
+        <v>7024001</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4306,7 +3929,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4317,6 +3940,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4333,10 +3981,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130180069</v>
+        <v>130180019</v>
       </c>
       <c r="B31" t="n">
-        <v>79211</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4344,34 +3992,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490566</v>
+        <v>490488</v>
       </c>
       <c r="R31" t="n">
-        <v>7023937</v>
+        <v>7023990</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4408,7 +4064,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4419,6 +4075,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4435,52 +4116,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130180042</v>
+        <v>130180020</v>
       </c>
       <c r="B32" t="n">
-        <v>80345</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490679</v>
+        <v>490494</v>
       </c>
       <c r="R32" t="n">
-        <v>7023796</v>
+        <v>7023983</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4517,7 +4203,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>Ringhack (savhack), färska, i mycket riklig mängd längs minst 8 meter på en granstam. Troligen skapade under ringhackningssäsongen 2025.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4526,7 +4212,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4537,22 +4222,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4570,10 +4255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130180033</v>
+        <v>130180021</v>
       </c>
       <c r="B33" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4603,7 +4288,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4613,10 +4298,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490591</v>
+        <v>490508</v>
       </c>
       <c r="R33" t="n">
-        <v>7023786</v>
+        <v>7023972</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4653,7 +4338,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en hyfsst grov gran en bit innanför en hyggeskant.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4705,10 +4390,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130180009</v>
+        <v>130180022</v>
       </c>
       <c r="B34" t="n">
-        <v>91761</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4716,28 +4401,29 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4747,10 +4433,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490651</v>
+        <v>490522</v>
       </c>
       <c r="R34" t="n">
-        <v>7024020</v>
+        <v>7023957</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4787,7 +4473,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>I en granlåga i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4796,7 +4482,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4817,12 +4502,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4840,10 +4525,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130180027</v>
+        <v>130180023</v>
       </c>
       <c r="B35" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4876,21 +4561,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490539</v>
+        <v>490509</v>
       </c>
       <c r="R35" t="n">
-        <v>7023923</v>
+        <v>7023962</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4927,7 +4608,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4979,10 +4660,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130180059</v>
+        <v>130180024</v>
       </c>
       <c r="B36" t="n">
-        <v>79211</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4990,34 +4671,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490614</v>
+        <v>490550</v>
       </c>
       <c r="R36" t="n">
-        <v>7023878</v>
+        <v>7023952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5054,7 +4743,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid körspår.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5065,6 +4754,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5081,10 +4795,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130180063</v>
+        <v>130180025</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5092,34 +4806,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490561</v>
+        <v>490547</v>
       </c>
       <c r="R37" t="n">
-        <v>7023986</v>
+        <v>7023930</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5156,7 +4878,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5167,6 +4889,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5183,10 +4930,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130180065</v>
+        <v>130180026</v>
       </c>
       <c r="B38" t="n">
-        <v>79211</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,34 +4941,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490576</v>
+        <v>490539</v>
       </c>
       <c r="R38" t="n">
-        <v>7023998</v>
+        <v>7023926</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5258,7 +5013,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5269,6 +5024,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5285,10 +5065,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130180016</v>
+        <v>130180027</v>
       </c>
       <c r="B39" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5321,17 +5101,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490471</v>
+        <v>490539</v>
       </c>
       <c r="R39" t="n">
-        <v>7024008</v>
+        <v>7023923</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5368,7 +5152,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en något grövre gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, längs några meter på en gran med dubbeltopp.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5382,7 +5166,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5420,10 +5204,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130180025</v>
+        <v>130180028</v>
       </c>
       <c r="B40" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5453,7 +5237,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5463,10 +5247,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490547</v>
+        <v>490534</v>
       </c>
       <c r="R40" t="n">
-        <v>7023930</v>
+        <v>7023897</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5503,7 +5287,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5555,10 +5339,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130180035</v>
+        <v>130180029</v>
       </c>
       <c r="B41" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5591,17 +5375,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490603</v>
+        <v>490543</v>
       </c>
       <c r="R41" t="n">
-        <v>7023797</v>
+        <v>7023888</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5638,7 +5426,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
+          <t>Ringhack (savhack), färska, i god mängd på en gran vid en hyggeskant. Troligen  skapade 2025.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5690,10 +5478,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130180034</v>
+        <v>130180030</v>
       </c>
       <c r="B42" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5733,10 +5521,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490609</v>
+        <v>490538</v>
       </c>
       <c r="R42" t="n">
-        <v>7023788</v>
+        <v>7023883</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5773,7 +5561,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5825,10 +5613,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130180077</v>
+        <v>130180031</v>
       </c>
       <c r="B43" t="n">
-        <v>79211</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5836,34 +5624,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490626</v>
+        <v>490546</v>
       </c>
       <c r="R43" t="n">
-        <v>7023902</v>
+        <v>7023885</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5900,7 +5700,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Enstaka på gran i äldre barrblandskog.</t>
+          <t>Ringhack (savhack), färska, i god mängd längs några meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5911,6 +5711,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5927,10 +5752,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130180068</v>
+        <v>130180032</v>
       </c>
       <c r="B44" t="n">
-        <v>79211</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5938,34 +5763,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490541</v>
+        <v>490566</v>
       </c>
       <c r="R44" t="n">
-        <v>7023968</v>
+        <v>7023832</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6002,7 +5839,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på en smal gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6013,6 +5850,31 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6029,10 +5891,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130180062</v>
+        <v>130180033</v>
       </c>
       <c r="B45" t="n">
-        <v>79211</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6040,34 +5902,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490550</v>
+        <v>490591</v>
       </c>
       <c r="R45" t="n">
-        <v>7023998</v>
+        <v>7023786</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6104,7 +5974,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6115,6 +5985,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6131,10 +6026,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130180060</v>
+        <v>130180034</v>
       </c>
       <c r="B46" t="n">
-        <v>79211</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6142,34 +6037,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490647</v>
+        <v>490609</v>
       </c>
       <c r="R46" t="n">
-        <v>7023943</v>
+        <v>7023788</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6206,7 +6109,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack (savhack), färska, enstaka ca 5-6 meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6217,6 +6120,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6233,10 +6161,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130180037</v>
+        <v>130180035</v>
       </c>
       <c r="B47" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6266,7 +6194,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6276,10 +6204,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490575</v>
+        <v>490603</v>
       </c>
       <c r="R47" t="n">
-        <v>7023818</v>
+        <v>7023797</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6316,7 +6244,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, ett par meter upp på en levande gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6368,38 +6296,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130180045</v>
+        <v>130180036</v>
       </c>
       <c r="B48" t="n">
-        <v>97828</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6407,10 +6339,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490515</v>
+        <v>490589</v>
       </c>
       <c r="R48" t="n">
-        <v>7024010</v>
+        <v>7023793</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6447,7 +6379,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6456,13 +6388,32 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6480,10 +6431,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130180075</v>
+        <v>130180037</v>
       </c>
       <c r="B49" t="n">
-        <v>79211</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6491,34 +6442,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490602</v>
+        <v>490575</v>
       </c>
       <c r="R49" t="n">
-        <v>7023937</v>
+        <v>7023818</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6555,7 +6514,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gran i äldre barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6566,6 +6525,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6582,10 +6566,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130180067</v>
+        <v>130180038</v>
       </c>
       <c r="B50" t="n">
-        <v>79211</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6593,34 +6577,46 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490505</v>
+        <v>490648</v>
       </c>
       <c r="R50" t="n">
-        <v>7023981</v>
+        <v>7023846</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6657,17 +6653,47 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Gamla bohål i en stående död gran med full längd som har fruktkroppar av granticka. Ett bohål (diameter 4 cm) på 1,8 meters höjd, och ett bohål (diameter 4,5 cm) på 2,1 meters höjd. Finns även fler bohål och andra hackade hål högre upp i granstammen. Troligen bohål som tidigare använts av tretåig hackspett. Hålens storlek och att en hona av tretåig hackspett födosökte precis intill styrker detta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6684,10 +6710,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130180026</v>
+        <v>130180039</v>
       </c>
       <c r="B51" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6712,25 +6738,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490539</v>
+        <v>490650</v>
       </c>
       <c r="R51" t="n">
-        <v>7023926</v>
+        <v>7023840</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6767,7 +6805,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>1 hona som födosökte bland annat på en stående död/döende gran med full längd och 44 cm i brösthöjdsdiameter. På fyndplatsen finns en volym av stående död ved främst av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. En provyta för att bedöma livsmiljövärdet här ger minst 410 poäng.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6784,6 +6822,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad barrblandskog med rikliga mängder stående död ved.</t>
+        </is>
+      </c>
       <c r="AJ51" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6796,12 +6839,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6819,10 +6862,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130180043</v>
+        <v>130180040</v>
       </c>
       <c r="B52" t="n">
-        <v>57851</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6830,16 +6873,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6847,33 +6890,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490588</v>
+        <v>490609</v>
       </c>
       <c r="R52" t="n">
-        <v>7023887</v>
+        <v>7023756</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6910,7 +6945,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>1 individ med lockläte hördes här i skogen. En bit längre bort hördes en annan individ av spillkråka.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6927,9 +6962,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog med gott om stående död ved.</t>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6947,49 +6992,61 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130180044</v>
+        <v>130180041</v>
       </c>
       <c r="B53" t="n">
-        <v>97828</v>
+        <v>58114</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Höglunda Väst, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490663</v>
+        <v>490626</v>
       </c>
       <c r="R53" t="n">
-        <v>7024019</v>
+        <v>7023887</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7026,7 +7083,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>I barrblandskog.</t>
+          <t>Minst 1 individ, ev. fler. Fyndplatsen finns i flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7035,13 +7092,17 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7059,42 +7120,38 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130180030</v>
+        <v>130180044</v>
       </c>
       <c r="B54" t="n">
-        <v>57854</v>
+        <v>97983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7102,10 +7159,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490538</v>
+        <v>490663</v>
       </c>
       <c r="R54" t="n">
-        <v>7023883</v>
+        <v>7024019</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7142,7 +7199,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7151,32 +7208,13 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7194,42 +7232,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130180024</v>
+        <v>130180045</v>
       </c>
       <c r="B55" t="n">
-        <v>57854</v>
+        <v>97983</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7237,10 +7271,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490550</v>
+        <v>490515</v>
       </c>
       <c r="R55" t="n">
-        <v>7023952</v>
+        <v>7024010</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7277,7 +7311,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid körspår.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7286,32 +7320,13 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7329,37 +7344,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130180052</v>
+        <v>130180046</v>
       </c>
       <c r="B56" t="n">
-        <v>91781</v>
+        <v>97983</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7367,10 +7383,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490615</v>
+        <v>490513</v>
       </c>
       <c r="R56" t="n">
-        <v>7023767</v>
+        <v>7023984</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7407,7 +7423,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>I stubbe och låga av knäckt gran.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7423,26 +7439,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7460,42 +7456,38 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130180015</v>
+        <v>130180047</v>
       </c>
       <c r="B57" t="n">
-        <v>57854</v>
+        <v>97983</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7503,10 +7495,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490474</v>
+        <v>490586</v>
       </c>
       <c r="R57" t="n">
-        <v>7024009</v>
+        <v>7023926</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7543,7 +7535,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I barrblandskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7552,32 +7544,13 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7592,349 +7565,6 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>130180032</v>
-      </c>
-      <c r="B58" t="n">
-        <v>57854</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Höglunda Väst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>490566</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7023832</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, enstaka på en smal gran vid en hyggeskant.</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>130180066</v>
-      </c>
-      <c r="B59" t="n">
-        <v>79211</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Höglunda Väst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>490497</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7024012</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>130180076</v>
-      </c>
-      <c r="B60" t="n">
-        <v>79211</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Höglunda Väst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>490653</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7023898</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På gran intill andra hänglavar, i barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56648-2025 artfynd.xlsx
+++ b/artfynd/A 56648-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180008</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -942,6 +952,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180009</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1044,6 +1059,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180059</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180060</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180061</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1379,6 +1409,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180062</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1481,6 +1516,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180063</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1583,6 +1623,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180064</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1685,6 +1730,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180065</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180066</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180067</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1991,6 +2051,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180068</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180069</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2224,6 +2294,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180070</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2326,6 +2401,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180071</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2428,6 +2508,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180072</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2530,6 +2615,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180073</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2632,6 +2722,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180074</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2734,6 +2829,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180075</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2836,6 +2936,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180076</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2938,6 +3043,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180077</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3040,6 +3150,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180078</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3175,6 +3290,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180042</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3303,6 +3423,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180043</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3438,6 +3563,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180014</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3573,6 +3703,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180015</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3708,6 +3843,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180016</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3843,6 +3983,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180017</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3978,6 +4123,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180018</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4113,6 +4263,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180019</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4252,6 +4407,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180020</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4387,6 +4547,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180021</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4522,6 +4687,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180022</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4657,6 +4827,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180023</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4792,6 +4967,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180024</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4927,6 +5107,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5062,6 +5247,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180026</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5201,6 +5391,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180027</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5336,6 +5531,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180028</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5475,6 +5675,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180029</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5610,6 +5815,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180030</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5749,6 +5959,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180031</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5888,6 +6103,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180032</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6023,6 +6243,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180033</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6158,6 +6383,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180034</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6293,6 +6523,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180035</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6428,6 +6663,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180036</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6563,6 +6803,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180037</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6707,6 +6952,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180038</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6859,6 +7109,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180039</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6989,6 +7244,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180040</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7117,6 +7377,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180041</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7229,6 +7494,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180044</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7341,6 +7611,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180045</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7453,6 +7728,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180046</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7565,8 +7845,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180047</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>